--- a/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="89">
   <si>
     <t>Scenario</t>
   </si>
@@ -94,211 +94,190 @@
     <t>Haryana</t>
   </si>
   <si>
-    <t>Punjab</t>
+    <t>AMRITSAR</t>
+  </si>
+  <si>
+    <t>FAZILKA</t>
   </si>
   <si>
     <t>JALANDHAR</t>
   </si>
   <si>
-    <t>FAZILKA</t>
+    <t>SRI MUKTSAR SAHIB</t>
+  </si>
+  <si>
+    <t>TARN TARAN</t>
+  </si>
+  <si>
+    <t>Stor</t>
+  </si>
+  <si>
+    <t>CHAK SAKANDAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHILOWAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHIUWALA DHAB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAMKOT GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
+  </si>
+  <si>
+    <t>BHAGSAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAHABADAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>sri muktsar sahib grain market</t>
+  </si>
+  <si>
+    <t>KARAM PATTI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHALRA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Depot</t>
+  </si>
+  <si>
+    <t>agah</t>
   </si>
   <si>
     <t>MALERKOTLA</t>
-  </si>
-  <si>
-    <t>SRI MUKTSAR SAHIB</t>
-  </si>
-  <si>
-    <t>ADAMPUR</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>AHMEDGARH</t>
-  </si>
-  <si>
-    <t>Malout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GADA DOB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KALAR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUMBAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NARAINPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SITO GUNO GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHIKHAMPUR BEGOWAL</t>
-  </si>
-  <si>
-    <t>DHALER KHURD</t>
-  </si>
-  <si>
-    <t>KANGANWAL</t>
-  </si>
-  <si>
-    <t>KUP</t>
-  </si>
-  <si>
-    <t>MAHOLI KALAN</t>
-  </si>
-  <si>
-    <t>MANAK HERI</t>
-  </si>
-  <si>
-    <t>MOMNA BAD</t>
-  </si>
-  <si>
-    <t>UMARPURA (NATHUMAJRA)</t>
-  </si>
-  <si>
-    <t>KARAM PATTI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>agah</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -659,7 +638,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -744,64 +723,64 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>31</v>
       </c>
       <c r="F2">
-        <v>1046</v>
+        <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H2">
-        <v>31.425406</v>
+        <v>31.84430551</v>
       </c>
       <c r="I2">
-        <v>75.719528</v>
+        <v>74.91208039999999</v>
       </c>
       <c r="J2">
-        <v>522</v>
+        <v>393</v>
       </c>
       <c r="K2">
-        <v>31.4204409</v>
+        <v>31.863261</v>
       </c>
       <c r="L2">
-        <v>75.69994199999999</v>
+        <v>74.945286</v>
       </c>
       <c r="M2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N2">
-        <v>625</v>
+        <v>3</v>
       </c>
       <c r="O2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R2" t="s">
         <v>31</v>
       </c>
       <c r="S2">
-        <v>31.408658</v>
+        <v>31.8529346</v>
       </c>
       <c r="T2">
-        <v>75.685958</v>
+        <v>74.91584450000001</v>
       </c>
       <c r="U2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V2">
-        <v>21500</v>
+        <v>50000</v>
       </c>
       <c r="W2">
-        <v>4.4325</v>
+        <v>8.6297</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -815,64 +794,64 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>501</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H3">
-        <v>30.156605</v>
+        <v>31.7398221</v>
       </c>
       <c r="I3">
-        <v>74.19572100000001</v>
+        <v>74.6072853</v>
       </c>
       <c r="J3">
-        <v>280</v>
+        <v>4</v>
       </c>
       <c r="K3">
-        <v>30.154922</v>
+        <v>31.781936</v>
       </c>
       <c r="L3">
-        <v>74.193507</v>
+        <v>74.76758049999999</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N3">
-        <v>396</v>
+        <v>5</v>
       </c>
       <c r="O3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S3">
-        <v>30.15881226</v>
+        <v>31.800077</v>
       </c>
       <c r="T3">
-        <v>74.18214294000001</v>
+        <v>74.588493</v>
       </c>
       <c r="U3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V3">
-        <v>90000</v>
+        <v>50000</v>
       </c>
       <c r="W3">
-        <v>2.1146</v>
+        <v>52.445</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -886,16 +865,16 @@
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>501</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4">
         <v>30.156605</v>
@@ -904,46 +883,46 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J4">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="K4">
-        <v>30.15894356</v>
+        <v>30.154922</v>
       </c>
       <c r="L4">
-        <v>74.18094151</v>
+        <v>74.193507</v>
       </c>
       <c r="M4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N4">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="O4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P4" t="s">
         <v>25</v>
       </c>
       <c r="Q4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S4">
-        <v>30.15894356</v>
+        <v>30.15881226</v>
       </c>
       <c r="T4">
-        <v>74.18094151</v>
+        <v>74.18214294000001</v>
       </c>
       <c r="U4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V4">
-        <v>60000</v>
+        <v>90000</v>
       </c>
       <c r="W4">
-        <v>1.7881</v>
+        <v>2.1146</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -957,16 +936,16 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>501</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5">
         <v>30.156605</v>
@@ -984,37 +963,37 @@
         <v>74.18094151</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N5">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S5">
-        <v>30.15848535</v>
+        <v>30.15894356</v>
       </c>
       <c r="T5">
-        <v>74.18085842000001</v>
+        <v>74.18094151</v>
       </c>
       <c r="U5" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V5">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="W5">
-        <v>2.0996</v>
+        <v>1.7881</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1028,16 +1007,16 @@
         <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6">
         <v>501</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H6">
         <v>30.156605</v>
@@ -1055,37 +1034,37 @@
         <v>74.18094151</v>
       </c>
       <c r="M6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N6">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S6">
-        <v>30.15809938</v>
+        <v>30.15848535</v>
       </c>
       <c r="T6">
-        <v>74.16401603</v>
+        <v>74.18085842000001</v>
       </c>
       <c r="U6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V6">
-        <v>145397</v>
+        <v>120000</v>
       </c>
       <c r="W6">
-        <v>3.8129</v>
+        <v>2.0996</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1099,16 +1078,16 @@
         <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7">
         <v>501</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H7">
         <v>30.156605</v>
@@ -1117,46 +1096,46 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="K7">
-        <v>30.163017</v>
+        <v>30.15894356</v>
       </c>
       <c r="L7">
-        <v>74.186234</v>
+        <v>74.18094151</v>
       </c>
       <c r="M7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N7">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S7">
-        <v>30.1689126</v>
+        <v>30.15809938</v>
       </c>
       <c r="T7">
-        <v>74.183232</v>
+        <v>74.16401603</v>
       </c>
       <c r="U7" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V7">
-        <v>31477</v>
+        <v>33610</v>
       </c>
       <c r="W7">
-        <v>3.5095</v>
+        <v>3.8129</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1170,16 +1149,16 @@
         <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8">
         <v>501</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H8">
         <v>30.156605</v>
@@ -1197,22 +1176,22 @@
         <v>74.193507</v>
       </c>
       <c r="M8" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N8">
         <v>405</v>
       </c>
       <c r="O8" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S8">
         <v>30.15857797</v>
@@ -1221,7 +1200,7 @@
         <v>74.18315728</v>
       </c>
       <c r="U8" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V8">
         <v>150000</v>
@@ -1241,22 +1220,22 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H9">
-        <v>30.099748</v>
+        <v>30.156605</v>
       </c>
       <c r="I9">
-        <v>74.34759699999999</v>
+        <v>74.19572100000001</v>
       </c>
       <c r="J9">
         <v>287</v>
@@ -1268,22 +1247,22 @@
         <v>74.161942</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N9">
         <v>407</v>
       </c>
       <c r="O9" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S9">
         <v>30.126927</v>
@@ -1292,13 +1271,13 @@
         <v>74.161942</v>
       </c>
       <c r="U9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V9">
-        <v>71835.5</v>
+        <v>143264</v>
       </c>
       <c r="W9">
-        <v>25.357</v>
+        <v>9.338900000000001</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1312,64 +1291,64 @@
         <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I10">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J10">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K10">
-        <v>30.105887</v>
+        <v>30.090357</v>
       </c>
       <c r="L10">
-        <v>74.18092900000001</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M10" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N10">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="O10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S10">
-        <v>30.10552983</v>
+        <v>30.08793156</v>
       </c>
       <c r="T10">
-        <v>74.18014506</v>
+        <v>74.20908439</v>
       </c>
       <c r="U10" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V10">
-        <v>73538.5</v>
+        <v>48247.5</v>
       </c>
       <c r="W10">
-        <v>13.9231</v>
+        <v>24.2685</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1383,64 +1362,64 @@
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F11">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I11">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J11">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K11">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L11">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M11" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N11">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O11" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S11">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T11">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U11" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V11">
-        <v>322</v>
+        <v>23588</v>
       </c>
       <c r="W11">
-        <v>15.4219</v>
+        <v>23.3062</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -1454,64 +1433,64 @@
         <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F12">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H12">
-        <v>30.162859</v>
+        <v>30.028699</v>
       </c>
       <c r="I12">
-        <v>73.991192</v>
+        <v>74.197309</v>
       </c>
       <c r="J12">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K12">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L12">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M12" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N12">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S12">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T12">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V12">
-        <v>37309</v>
+        <v>73860.5</v>
       </c>
       <c r="W12">
-        <v>22.8658</v>
+        <v>13.9231</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -1525,64 +1504,64 @@
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="H13">
-        <v>30.16948</v>
+        <v>30.162859</v>
       </c>
       <c r="I13">
-        <v>74.28432100000001</v>
+        <v>73.991192</v>
       </c>
       <c r="J13">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K13">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L13">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N13">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S13">
-        <v>30.1689126</v>
+        <v>30.126927</v>
       </c>
       <c r="T13">
-        <v>74.183232</v>
+        <v>74.161942</v>
       </c>
       <c r="U13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V13">
-        <v>2823</v>
+        <v>37309</v>
       </c>
       <c r="W13">
-        <v>12.4872</v>
+        <v>22.8658</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -1596,16 +1575,16 @@
         <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14">
         <v>506</v>
       </c>
       <c r="G14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H14">
         <v>30.16948</v>
@@ -1614,46 +1593,46 @@
         <v>74.28432100000001</v>
       </c>
       <c r="J14">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K14">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L14">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N14">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O14" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S14">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T14">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U14" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V14">
-        <v>15202.5</v>
+        <v>18025.5</v>
       </c>
       <c r="W14">
-        <v>12.3346</v>
+        <v>15.4394</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -1667,16 +1646,16 @@
         <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15">
         <v>507</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H15">
         <v>30.034436</v>
@@ -1694,37 +1673,37 @@
         <v>74.20853700000001</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N15">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O15" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S15">
-        <v>30.08675444</v>
+        <v>30.08793156</v>
       </c>
       <c r="T15">
-        <v>74.20888524</v>
+        <v>74.20908439</v>
       </c>
       <c r="U15" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V15">
-        <v>49766</v>
+        <v>16177.5</v>
       </c>
       <c r="W15">
-        <v>8.3849</v>
+        <v>8.2553</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -1738,64 +1717,64 @@
         <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H16">
-        <v>30.182524</v>
+        <v>30.034436</v>
       </c>
       <c r="I16">
-        <v>74.326095</v>
+        <v>74.233859</v>
       </c>
       <c r="J16">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="K16">
-        <v>30.163017</v>
+        <v>30.090357</v>
       </c>
       <c r="L16">
-        <v>74.186234</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N16">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="O16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S16">
-        <v>30.16991135</v>
+        <v>30.08675444</v>
       </c>
       <c r="T16">
-        <v>74.18230296</v>
+        <v>74.20888524</v>
       </c>
       <c r="U16" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V16">
-        <v>41707.5</v>
+        <v>33588.5</v>
       </c>
       <c r="W16">
-        <v>17.6794</v>
+        <v>8.3849</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -1809,64 +1788,64 @@
         <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H17">
-        <v>30.199756</v>
+        <v>30.182524</v>
       </c>
       <c r="I17">
-        <v>74.108656</v>
+        <v>74.326095</v>
       </c>
       <c r="J17">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K17">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L17">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N17">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O17" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S17">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T17">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U17" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V17">
-        <v>18038</v>
+        <v>13129</v>
       </c>
       <c r="W17">
-        <v>12.7486</v>
+        <v>17.832</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -1880,22 +1859,22 @@
         <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G18" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>30.113508</v>
+        <v>30.182524</v>
       </c>
       <c r="I18">
-        <v>73.989543</v>
+        <v>74.326095</v>
       </c>
       <c r="J18">
         <v>287</v>
@@ -1907,22 +1886,22 @@
         <v>74.161942</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N18">
         <v>407</v>
       </c>
       <c r="O18" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S18">
         <v>30.126927</v>
@@ -1931,13 +1910,13 @@
         <v>74.161942</v>
       </c>
       <c r="U18" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V18">
-        <v>44568.5</v>
+        <v>28578.5</v>
       </c>
       <c r="W18">
-        <v>18.7185</v>
+        <v>20.7843</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -1951,64 +1930,64 @@
         <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F19">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="G19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="H19">
-        <v>30.122605</v>
+        <v>30.199756</v>
       </c>
       <c r="I19">
-        <v>74.328892</v>
+        <v>74.108656</v>
       </c>
       <c r="J19">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K19">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L19">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M19" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N19">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O19" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S19">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T19">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U19" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V19">
-        <v>25216</v>
+        <v>18038</v>
       </c>
       <c r="W19">
-        <v>24.8328</v>
+        <v>12.7486</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2022,64 +2001,64 @@
         <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H20">
-        <v>30.237206</v>
+        <v>30.113508</v>
       </c>
       <c r="I20">
-        <v>74.23982700000001</v>
+        <v>73.989543</v>
       </c>
       <c r="J20">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K20">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L20">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M20" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N20">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O20" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S20">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T20">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V20">
-        <v>44802</v>
+        <v>44568.5</v>
       </c>
       <c r="W20">
-        <v>14.497</v>
+        <v>18.7185</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2093,64 +2072,64 @@
         <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="G21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H21">
-        <v>30.023582</v>
+        <v>30.122605</v>
       </c>
       <c r="I21">
-        <v>74.04262799999999</v>
+        <v>74.328892</v>
       </c>
       <c r="J21">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K21">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L21">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M21" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N21">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O21" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S21">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T21">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U21" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V21">
-        <v>30276.5</v>
+        <v>25216</v>
       </c>
       <c r="W21">
-        <v>22.7583</v>
+        <v>22.782</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2164,64 +2143,64 @@
         <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="G22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H22">
-        <v>29.960526</v>
+        <v>30.237206</v>
       </c>
       <c r="I22">
-        <v>74.219824</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J22">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K22">
-        <v>30.105887</v>
+        <v>30.175344</v>
       </c>
       <c r="L22">
-        <v>74.18092900000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M22" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N22">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="O22" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S22">
-        <v>30.10552983</v>
+        <v>30.17081207</v>
       </c>
       <c r="T22">
-        <v>74.18014506</v>
+        <v>74.18179719</v>
       </c>
       <c r="U22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V22">
-        <v>19961.5</v>
+        <v>44802</v>
       </c>
       <c r="W22">
-        <v>23.4263</v>
+        <v>14.497</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -2235,64 +2214,64 @@
         <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F23">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="G23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H23">
-        <v>30.082625</v>
+        <v>30.023582</v>
       </c>
       <c r="I23">
-        <v>74.288794</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J23">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K23">
-        <v>30.100105</v>
+        <v>30.126927</v>
       </c>
       <c r="L23">
-        <v>74.20670699999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N23">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O23" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
       </c>
       <c r="Q23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R23" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S23">
-        <v>30.0974593</v>
+        <v>30.126927</v>
       </c>
       <c r="T23">
-        <v>74.206666</v>
+        <v>74.161942</v>
       </c>
       <c r="U23" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V23">
-        <v>9709</v>
+        <v>30276.5</v>
       </c>
       <c r="W23">
-        <v>13.8965</v>
+        <v>22.7583</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -2306,64 +2285,64 @@
         <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F24">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G24" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H24">
-        <v>30.082625</v>
+        <v>29.960526</v>
       </c>
       <c r="I24">
-        <v>74.288794</v>
+        <v>74.219824</v>
       </c>
       <c r="J24">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K24">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L24">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M24" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N24">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="O24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S24">
-        <v>30.126927</v>
+        <v>30.08675444</v>
       </c>
       <c r="T24">
-        <v>74.161942</v>
+        <v>74.20888524</v>
       </c>
       <c r="U24" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V24">
-        <v>54672</v>
+        <v>19961.5</v>
       </c>
       <c r="W24">
-        <v>15.9473</v>
+        <v>17.3584</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -2377,64 +2356,64 @@
         <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G25" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H25">
-        <v>30.221432</v>
+        <v>30.082625</v>
       </c>
       <c r="I25">
-        <v>74.35153099999999</v>
+        <v>74.288794</v>
       </c>
       <c r="J25">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K25">
-        <v>30.175344</v>
+        <v>30.090357</v>
       </c>
       <c r="L25">
-        <v>74.178363</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N25">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="O25" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S25">
-        <v>30.17081207</v>
+        <v>30.08793156</v>
       </c>
       <c r="T25">
-        <v>74.18179719</v>
+        <v>74.20908439</v>
       </c>
       <c r="U25" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V25">
-        <v>13755.5</v>
+        <v>64381</v>
       </c>
       <c r="W25">
-        <v>27.7616</v>
+        <v>14.8588</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -2448,64 +2427,64 @@
         <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G26" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H26">
-        <v>30.221432</v>
+        <v>30.254598</v>
       </c>
       <c r="I26">
-        <v>74.35153099999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J26">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K26">
-        <v>30.163017</v>
+        <v>30.180346</v>
       </c>
       <c r="L26">
-        <v>74.186234</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M26" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N26">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="O26" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S26">
-        <v>30.16991135</v>
+        <v>30.15809938</v>
       </c>
       <c r="T26">
-        <v>74.18230296</v>
+        <v>74.16401603</v>
       </c>
       <c r="U26" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V26">
-        <v>6714.5</v>
+        <v>39817.5</v>
       </c>
       <c r="W26">
-        <v>26.1737</v>
+        <v>13.1818</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -2519,64 +2498,64 @@
         <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F27">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H27">
-        <v>30.254598</v>
+        <v>30.173582</v>
       </c>
       <c r="I27">
-        <v>74.124285</v>
+        <v>74.250483</v>
       </c>
       <c r="J27">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K27">
-        <v>30.180346</v>
+        <v>30.163017</v>
       </c>
       <c r="L27">
-        <v>74.17439299999999</v>
+        <v>74.186234</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N27">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="O27" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S27">
-        <v>30.15809938</v>
+        <v>30.1689126</v>
       </c>
       <c r="T27">
-        <v>74.16401603</v>
+        <v>74.183232</v>
       </c>
       <c r="U27" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V27">
-        <v>39817.5</v>
+        <v>10375.5</v>
       </c>
       <c r="W27">
-        <v>13.1818</v>
+        <v>11.3262</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -2590,64 +2569,64 @@
         <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F28">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H28">
-        <v>30.173582</v>
+        <v>30.21019</v>
       </c>
       <c r="I28">
-        <v>74.250483</v>
+        <v>74.024728</v>
       </c>
       <c r="J28">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K28">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L28">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M28" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N28">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O28" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R28" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S28">
-        <v>30.16991135</v>
+        <v>30.126927</v>
       </c>
       <c r="T28">
-        <v>74.18230296</v>
+        <v>74.161942</v>
       </c>
       <c r="U28" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V28">
-        <v>10375.5</v>
+        <v>100949.5</v>
       </c>
       <c r="W28">
-        <v>11.1736</v>
+        <v>20.9825</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -2661,22 +2640,22 @@
         <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H29">
-        <v>30.21019</v>
+        <v>30.257887</v>
       </c>
       <c r="I29">
-        <v>74.024728</v>
+        <v>74.185624</v>
       </c>
       <c r="J29">
         <v>285</v>
@@ -2688,37 +2667,37 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M29" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N29">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O29" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S29">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T29">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U29" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V29">
-        <v>72343</v>
+        <v>36622.5</v>
       </c>
       <c r="W29">
-        <v>21.7133</v>
+        <v>13.7053</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -2732,64 +2711,64 @@
         <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H30">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I30">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J30">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K30">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L30">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N30">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O30" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S30">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T30">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U30" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V30">
-        <v>28606.5</v>
+        <v>11652.5</v>
       </c>
       <c r="W30">
-        <v>20.9825</v>
+        <v>12.7417</v>
       </c>
     </row>
     <row r="31" spans="1:23">
@@ -2803,64 +2782,64 @@
         <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H31">
-        <v>30.257887</v>
+        <v>30.007285</v>
       </c>
       <c r="I31">
-        <v>74.185624</v>
+        <v>74.126166</v>
       </c>
       <c r="J31">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K31">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L31">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M31" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N31">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O31" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S31">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T31">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U31" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V31">
-        <v>2347.5</v>
+        <v>16592.5</v>
       </c>
       <c r="W31">
-        <v>13.7961</v>
+        <v>16.4176</v>
       </c>
     </row>
     <row r="32" spans="1:23">
@@ -2874,64 +2853,64 @@
         <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H32">
-        <v>30.257887</v>
+        <v>30.127701</v>
       </c>
       <c r="I32">
-        <v>74.185624</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J32">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K32">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L32">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M32" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N32">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="O32" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S32">
-        <v>30.17767461</v>
+        <v>30.126927</v>
       </c>
       <c r="T32">
-        <v>74.17723581</v>
+        <v>74.161942</v>
       </c>
       <c r="U32" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V32">
-        <v>34275</v>
+        <v>21311</v>
       </c>
       <c r="W32">
-        <v>13.7053</v>
+        <v>12.8099</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -2945,64 +2924,64 @@
         <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H33">
-        <v>30.007285</v>
+        <v>29.98347</v>
       </c>
       <c r="I33">
-        <v>74.126166</v>
+        <v>74.283652</v>
       </c>
       <c r="J33">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K33">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L33">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M33" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N33">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O33" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S33">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="T33">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="U33" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V33">
-        <v>28245</v>
+        <v>34094</v>
       </c>
       <c r="W33">
-        <v>16.4176</v>
+        <v>24.9691</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3016,64 +2995,64 @@
         <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H34">
-        <v>30.039412</v>
+        <v>30.216512</v>
       </c>
       <c r="I34">
-        <v>73.954567</v>
+        <v>74.269492</v>
       </c>
       <c r="J34">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K34">
-        <v>30.126927</v>
+        <v>30.163017</v>
       </c>
       <c r="L34">
-        <v>74.161942</v>
+        <v>74.186234</v>
       </c>
       <c r="M34" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N34">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="O34" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
       </c>
       <c r="Q34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S34">
-        <v>30.126927</v>
+        <v>30.1689126</v>
       </c>
       <c r="T34">
-        <v>74.161942</v>
+        <v>74.183232</v>
       </c>
       <c r="U34" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V34">
-        <v>12854</v>
+        <v>10795.5</v>
       </c>
       <c r="W34">
-        <v>24.3915</v>
+        <v>16.4895</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -3087,64 +3066,64 @@
         <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F35">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="G35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H35">
-        <v>30.012837</v>
+        <v>30.216512</v>
       </c>
       <c r="I35">
-        <v>74.432883</v>
+        <v>74.269492</v>
       </c>
       <c r="J35">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K35">
-        <v>30.090357</v>
+        <v>30.175344</v>
       </c>
       <c r="L35">
-        <v>74.20853700000001</v>
+        <v>74.178363</v>
       </c>
       <c r="M35" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N35">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="O35" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
       </c>
       <c r="Q35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R35" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S35">
-        <v>30.0974593</v>
+        <v>30.16991135</v>
       </c>
       <c r="T35">
-        <v>74.206666</v>
+        <v>74.18230296</v>
       </c>
       <c r="U35" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V35">
-        <v>74081</v>
+        <v>21605.5</v>
       </c>
       <c r="W35">
-        <v>33.5339</v>
+        <v>18.0371</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -3158,64 +3137,64 @@
         <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F36">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H36">
-        <v>30.127701</v>
+        <v>30.132598</v>
       </c>
       <c r="I36">
-        <v>74.06368999999999</v>
+        <v>74.343463</v>
       </c>
       <c r="J36">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="K36">
-        <v>30.126927</v>
+        <v>30.100105</v>
       </c>
       <c r="L36">
-        <v>74.161942</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M36" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N36">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="O36" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
       </c>
       <c r="Q36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R36" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S36">
-        <v>30.126927</v>
+        <v>30.0974593</v>
       </c>
       <c r="T36">
-        <v>74.161942</v>
+        <v>74.206666</v>
       </c>
       <c r="U36" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V36">
-        <v>21311</v>
+        <v>71196</v>
       </c>
       <c r="W36">
-        <v>12.8099</v>
+        <v>23.211</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -3229,64 +3208,64 @@
         <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F37">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="G37" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H37">
-        <v>29.98347</v>
+        <v>30.132598</v>
       </c>
       <c r="I37">
-        <v>74.283652</v>
+        <v>74.343463</v>
       </c>
       <c r="J37">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K37">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L37">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M37" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N37">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O37" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
       </c>
       <c r="Q37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R37" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S37">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T37">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U37" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V37">
-        <v>30310</v>
+        <v>2489</v>
       </c>
       <c r="W37">
-        <v>24.9691</v>
+        <v>25.2617</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -3300,64 +3279,64 @@
         <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F38">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H38">
-        <v>29.98347</v>
+        <v>30.065633</v>
       </c>
       <c r="I38">
-        <v>74.283652</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J38">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K38">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L38">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N38">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="O38" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
       </c>
       <c r="Q38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S38">
-        <v>30.08675444</v>
+        <v>30.126927</v>
       </c>
       <c r="T38">
-        <v>74.20888524</v>
+        <v>74.161942</v>
       </c>
       <c r="U38" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V38">
-        <v>3784</v>
+        <v>34208</v>
       </c>
       <c r="W38">
-        <v>25.0987</v>
+        <v>20.1886</v>
       </c>
     </row>
     <row r="39" spans="1:23">
@@ -3371,64 +3350,64 @@
         <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F39">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="G39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H39">
-        <v>30.216512</v>
+        <v>30.224829</v>
       </c>
       <c r="I39">
-        <v>74.269492</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J39">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K39">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="L39">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M39" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N39">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O39" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
       </c>
       <c r="Q39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S39">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="T39">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="U39" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V39">
-        <v>32401</v>
+        <v>54819.5</v>
       </c>
       <c r="W39">
-        <v>17.9247</v>
+        <v>12.7358</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -3442,22 +3421,22 @@
         <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F40">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H40">
-        <v>30.132598</v>
+        <v>30.178444</v>
       </c>
       <c r="I40">
-        <v>74.343463</v>
+        <v>74.065141</v>
       </c>
       <c r="J40">
         <v>287</v>
@@ -3469,22 +3448,22 @@
         <v>74.161942</v>
       </c>
       <c r="M40" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N40">
         <v>407</v>
       </c>
       <c r="O40" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
       </c>
       <c r="Q40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R40" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S40">
         <v>30.126927</v>
@@ -3493,13 +3472,13 @@
         <v>74.161942</v>
       </c>
       <c r="U40" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V40">
-        <v>73685</v>
+        <v>37768</v>
       </c>
       <c r="W40">
-        <v>25.2617</v>
+        <v>17.3585</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -3513,22 +3492,22 @@
         <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F41">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H41">
-        <v>30.065633</v>
+        <v>30.196706</v>
       </c>
       <c r="I41">
-        <v>73.98462499999999</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J41">
         <v>287</v>
@@ -3540,22 +3519,22 @@
         <v>74.161942</v>
       </c>
       <c r="M41" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N41">
         <v>407</v>
       </c>
       <c r="O41" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
       </c>
       <c r="Q41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R41" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S41">
         <v>30.126927</v>
@@ -3564,13 +3543,13 @@
         <v>74.161942</v>
       </c>
       <c r="U41" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V41">
-        <v>34208</v>
+        <v>29874.5</v>
       </c>
       <c r="W41">
-        <v>20.1886</v>
+        <v>18.316</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -3584,64 +3563,64 @@
         <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F42">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H42">
-        <v>29.956267</v>
+        <v>30.035803</v>
       </c>
       <c r="I42">
-        <v>74.332578</v>
+        <v>74.111367</v>
       </c>
       <c r="J42">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K42">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L42">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M42" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N42">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O42" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
       </c>
       <c r="Q42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R42" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S42">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T42">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U42" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V42">
-        <v>17701</v>
+        <v>56983.5</v>
       </c>
       <c r="W42">
-        <v>33.4485</v>
+        <v>15.5321</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -3655,64 +3634,64 @@
         <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F43">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="G43" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H43">
-        <v>30.224829</v>
+        <v>30.131281</v>
       </c>
       <c r="I43">
-        <v>74.12361199999999</v>
+        <v>74.103374</v>
       </c>
       <c r="J43">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K43">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L43">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M43" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N43">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O43" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
       </c>
       <c r="Q43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S43">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T43">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U43" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V43">
-        <v>54819.5</v>
+        <v>23195.5</v>
       </c>
       <c r="W43">
-        <v>12.7358</v>
+        <v>8.0145</v>
       </c>
     </row>
     <row r="44" spans="1:23">
@@ -3726,22 +3705,22 @@
         <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F44">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="G44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H44">
-        <v>30.178444</v>
+        <v>30.029455</v>
       </c>
       <c r="I44">
-        <v>74.065141</v>
+        <v>74.077962</v>
       </c>
       <c r="J44">
         <v>287</v>
@@ -3753,22 +3732,22 @@
         <v>74.161942</v>
       </c>
       <c r="M44" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N44">
         <v>407</v>
       </c>
       <c r="O44" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
       </c>
       <c r="Q44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S44">
         <v>30.126927</v>
@@ -3777,13 +3756,13 @@
         <v>74.161942</v>
       </c>
       <c r="U44" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V44">
-        <v>37768</v>
+        <v>57368</v>
       </c>
       <c r="W44">
-        <v>17.3585</v>
+        <v>21.5083</v>
       </c>
     </row>
     <row r="45" spans="1:23">
@@ -3797,64 +3776,64 @@
         <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F45">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H45">
-        <v>30.196706</v>
+        <v>29.983545</v>
       </c>
       <c r="I45">
-        <v>74.04839699999999</v>
+        <v>74.173574</v>
       </c>
       <c r="J45">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K45">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L45">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M45" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N45">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O45" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
       </c>
       <c r="Q45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S45">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T45">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U45" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V45">
-        <v>29874.5</v>
+        <v>2487</v>
       </c>
       <c r="W45">
-        <v>18.316</v>
+        <v>19.8493</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -3868,64 +3847,64 @@
         <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F46">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="G46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H46">
-        <v>30.035803</v>
+        <v>30.254422</v>
       </c>
       <c r="I46">
-        <v>74.111367</v>
+        <v>74.126414</v>
       </c>
       <c r="J46">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K46">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L46">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M46" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N46">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O46" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
       </c>
       <c r="Q46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S46">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T46">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U46" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V46">
-        <v>56983.5</v>
+        <v>29195</v>
       </c>
       <c r="W46">
-        <v>15.5321</v>
+        <v>12.9929</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -3939,64 +3918,64 @@
         <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F47">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="G47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H47">
-        <v>30.131281</v>
+        <v>30.247905</v>
       </c>
       <c r="I47">
-        <v>74.103374</v>
+        <v>74.129536</v>
       </c>
       <c r="J47">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K47">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L47">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M47" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N47">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O47" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
       </c>
       <c r="Q47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R47" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S47">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T47">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U47" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V47">
-        <v>23195.5</v>
+        <v>26795</v>
       </c>
       <c r="W47">
-        <v>8.0145</v>
+        <v>12.2155</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -4010,64 +3989,64 @@
         <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F48">
-        <v>536</v>
+        <v>543</v>
       </c>
       <c r="G48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H48">
-        <v>30.027734</v>
+        <v>30.25374</v>
       </c>
       <c r="I48">
-        <v>74.36728100000001</v>
+        <v>74.122122</v>
       </c>
       <c r="J48">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K48">
-        <v>30.090357</v>
+        <v>30.180346</v>
       </c>
       <c r="L48">
-        <v>74.20853700000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M48" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N48">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O48" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
       </c>
       <c r="Q48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R48" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S48">
-        <v>30.08793156</v>
+        <v>30.15809938</v>
       </c>
       <c r="T48">
-        <v>74.20908439</v>
+        <v>74.16401603</v>
       </c>
       <c r="U48" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V48">
-        <v>71340</v>
+        <v>7950</v>
       </c>
       <c r="W48">
-        <v>25.9835</v>
+        <v>13.4799</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -4081,64 +4060,64 @@
         <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F49">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H49">
-        <v>30.027734</v>
+        <v>29.975306</v>
       </c>
       <c r="I49">
-        <v>74.36728100000001</v>
+        <v>74.164011</v>
       </c>
       <c r="J49">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K49">
-        <v>30.090357</v>
+        <v>30.105887</v>
       </c>
       <c r="L49">
-        <v>74.20853700000001</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N49">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="O49" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
       </c>
       <c r="Q49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R49" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S49">
-        <v>30.0974593</v>
+        <v>30.10552983</v>
       </c>
       <c r="T49">
-        <v>74.206666</v>
+        <v>74.18014506</v>
       </c>
       <c r="U49" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V49">
-        <v>36210</v>
+        <v>5500</v>
       </c>
       <c r="W49">
-        <v>26.531</v>
+        <v>22.7863</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -4152,64 +4131,64 @@
         <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F50">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G50" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H50">
-        <v>29.951208</v>
+        <v>30.144184</v>
       </c>
       <c r="I50">
-        <v>74.380385</v>
+        <v>74.122771</v>
       </c>
       <c r="J50">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K50">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L50">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M50" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N50">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O50" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
       </c>
       <c r="Q50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R50" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S50">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T50">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U50" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V50">
-        <v>43549</v>
+        <v>12630.5</v>
       </c>
       <c r="W50">
-        <v>37.9375</v>
+        <v>7.2905</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -4223,22 +4202,22 @@
         <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F51">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H51">
-        <v>30.029455</v>
+        <v>30.161715</v>
       </c>
       <c r="I51">
-        <v>74.077962</v>
+        <v>73.987483</v>
       </c>
       <c r="J51">
         <v>287</v>
@@ -4250,22 +4229,22 @@
         <v>74.161942</v>
       </c>
       <c r="M51" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N51">
         <v>407</v>
       </c>
       <c r="O51" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
       </c>
       <c r="Q51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S51">
         <v>30.126927</v>
@@ -4274,13 +4253,13 @@
         <v>74.161942</v>
       </c>
       <c r="U51" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V51">
-        <v>57368</v>
+        <v>13803</v>
       </c>
       <c r="W51">
-        <v>21.5083</v>
+        <v>21.1098</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -4294,22 +4273,22 @@
         <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F52">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="G52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H52">
-        <v>29.983545</v>
+        <v>30.21135</v>
       </c>
       <c r="I52">
-        <v>74.173574</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J52">
         <v>287</v>
@@ -4321,22 +4300,22 @@
         <v>74.161942</v>
       </c>
       <c r="M52" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N52">
         <v>407</v>
       </c>
       <c r="O52" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
       </c>
       <c r="Q52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S52">
         <v>30.126927</v>
@@ -4345,13 +4324,13 @@
         <v>74.161942</v>
       </c>
       <c r="U52" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V52">
-        <v>2487</v>
+        <v>9145</v>
       </c>
       <c r="W52">
-        <v>21.3483</v>
+        <v>21.1286</v>
       </c>
     </row>
     <row r="53" spans="1:23">
@@ -4365,64 +4344,64 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F53">
-        <v>541</v>
+        <v>549</v>
       </c>
       <c r="G53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H53">
-        <v>30.254422</v>
+        <v>30.296726</v>
       </c>
       <c r="I53">
-        <v>74.126414</v>
+        <v>74.263169</v>
       </c>
       <c r="J53">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K53">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L53">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M53" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N53">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O53" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
       </c>
       <c r="Q53" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R53" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S53">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="T53">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="U53" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V53">
-        <v>29195</v>
+        <v>17622.5</v>
       </c>
       <c r="W53">
-        <v>12.9929</v>
+        <v>24.0567</v>
       </c>
     </row>
     <row r="54" spans="1:23">
@@ -4436,22 +4415,22 @@
         <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F54">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H54">
-        <v>30.247905</v>
+        <v>30.285139</v>
       </c>
       <c r="I54">
-        <v>74.129536</v>
+        <v>74.172681</v>
       </c>
       <c r="J54">
         <v>285</v>
@@ -4463,22 +4442,22 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M54" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N54">
         <v>400</v>
       </c>
       <c r="O54" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
       </c>
       <c r="Q54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R54" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S54">
         <v>30.15809938</v>
@@ -4487,13 +4466,13 @@
         <v>74.16401603</v>
       </c>
       <c r="U54" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V54">
-        <v>26795</v>
+        <v>2347.5</v>
       </c>
       <c r="W54">
-        <v>12.2155</v>
+        <v>18.2392</v>
       </c>
     </row>
     <row r="55" spans="1:23">
@@ -4507,22 +4486,22 @@
         <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F55">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="G55" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H55">
-        <v>30.25374</v>
+        <v>30.285139</v>
       </c>
       <c r="I55">
-        <v>74.122122</v>
+        <v>74.172681</v>
       </c>
       <c r="J55">
         <v>285</v>
@@ -4534,37 +4513,37 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M55" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N55">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
       </c>
       <c r="Q55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S55">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T55">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U55" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V55">
-        <v>7950</v>
+        <v>40337.5</v>
       </c>
       <c r="W55">
-        <v>13.4799</v>
+        <v>15.9344</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -4578,64 +4557,64 @@
         <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F56">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="G56" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H56">
-        <v>29.975306</v>
+        <v>30.260814</v>
       </c>
       <c r="I56">
-        <v>74.164011</v>
+        <v>74.269329</v>
       </c>
       <c r="J56">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K56">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L56">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M56" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N56">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O56" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
       </c>
       <c r="Q56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R56" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S56">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T56">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U56" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V56">
-        <v>5500</v>
+        <v>56502.5</v>
       </c>
       <c r="W56">
-        <v>24.2851</v>
+        <v>24.9286</v>
       </c>
     </row>
     <row r="57" spans="1:23">
@@ -4649,64 +4628,64 @@
         <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F57">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G57" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H57">
-        <v>30.144184</v>
+        <v>30.290503</v>
       </c>
       <c r="I57">
-        <v>74.122771</v>
+        <v>74.220803</v>
       </c>
       <c r="J57">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K57">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L57">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M57" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N57">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O57" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
       </c>
       <c r="Q57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S57">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T57">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U57" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V57">
-        <v>12630.5</v>
+        <v>43110</v>
       </c>
       <c r="W57">
-        <v>7.2905</v>
+        <v>20.8569</v>
       </c>
     </row>
     <row r="58" spans="1:23">
@@ -4720,64 +4699,64 @@
         <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F58">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G58" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H58">
-        <v>30.161715</v>
+        <v>30.251211</v>
       </c>
       <c r="I58">
-        <v>73.987483</v>
+        <v>74.011872</v>
       </c>
       <c r="J58">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K58">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L58">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M58" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N58">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O58" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
       </c>
       <c r="Q58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R58" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S58">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T58">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U58" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V58">
-        <v>13803</v>
+        <v>128218</v>
       </c>
       <c r="W58">
-        <v>21.1098</v>
+        <v>26.083</v>
       </c>
     </row>
     <row r="59" spans="1:23">
@@ -4791,22 +4770,22 @@
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F59">
-        <v>548</v>
+        <v>565</v>
       </c>
       <c r="G59" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H59">
-        <v>30.21135</v>
+        <v>30.280985</v>
       </c>
       <c r="I59">
-        <v>74.02397999999999</v>
+        <v>74.057811</v>
       </c>
       <c r="J59">
         <v>285</v>
@@ -4818,22 +4797,22 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M59" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N59">
         <v>400</v>
       </c>
       <c r="O59" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
       </c>
       <c r="Q59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R59" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S59">
         <v>30.15809938</v>
@@ -4842,13 +4821,13 @@
         <v>74.16401603</v>
       </c>
       <c r="U59" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V59">
-        <v>9145</v>
+        <v>62709.5</v>
       </c>
       <c r="W59">
-        <v>21.8595</v>
+        <v>23.0123</v>
       </c>
     </row>
     <row r="60" spans="1:23">
@@ -4862,22 +4841,22 @@
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F60">
-        <v>549</v>
+        <v>612</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H60">
-        <v>30.296726</v>
+        <v>30.3064</v>
       </c>
       <c r="I60">
-        <v>74.263169</v>
+        <v>74.22073899999999</v>
       </c>
       <c r="J60">
         <v>279</v>
@@ -4889,22 +4868,22 @@
         <v>74.178363</v>
       </c>
       <c r="M60" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N60">
         <v>401</v>
       </c>
       <c r="O60" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
       </c>
       <c r="Q60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R60" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S60">
         <v>30.17081207</v>
@@ -4913,13 +4892,13 @@
         <v>74.18179719</v>
       </c>
       <c r="U60" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V60">
-        <v>17622.5</v>
+        <v>47189.5</v>
       </c>
       <c r="W60">
-        <v>24.0567</v>
+        <v>22.6615</v>
       </c>
     </row>
     <row r="61" spans="1:23">
@@ -4936,37 +4915,37 @@
         <v>28</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F61">
-        <v>550</v>
+        <v>1046</v>
       </c>
       <c r="G61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H61">
-        <v>30.285139</v>
+        <v>31.425406</v>
       </c>
       <c r="I61">
-        <v>74.172681</v>
+        <v>75.719528</v>
       </c>
       <c r="J61">
-        <v>285</v>
+        <v>522</v>
       </c>
       <c r="K61">
-        <v>30.180346</v>
+        <v>31.4204409</v>
       </c>
       <c r="L61">
-        <v>74.17439299999999</v>
+        <v>75.69994199999999</v>
       </c>
       <c r="M61" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N61">
-        <v>402</v>
+        <v>625</v>
       </c>
       <c r="O61" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -4975,22 +4954,22 @@
         <v>28</v>
       </c>
       <c r="R61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S61">
-        <v>30.17767461</v>
+        <v>31.408658</v>
       </c>
       <c r="T61">
-        <v>74.17723581</v>
+        <v>75.685958</v>
       </c>
       <c r="U61" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V61">
-        <v>42685</v>
+        <v>21500</v>
       </c>
       <c r="W61">
-        <v>15.9344</v>
+        <v>4.4325</v>
       </c>
     </row>
     <row r="62" spans="1:23">
@@ -5004,64 +4983,64 @@
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F62">
-        <v>551</v>
+        <v>1577</v>
       </c>
       <c r="G62" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H62">
-        <v>30.260814</v>
+        <v>30.4426709</v>
       </c>
       <c r="I62">
-        <v>74.269329</v>
+        <v>74.4101264</v>
       </c>
       <c r="J62">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K62">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L62">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M62" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N62">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="O62" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
       </c>
       <c r="Q62" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="R62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S62">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T62">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U62" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V62">
-        <v>56502.5</v>
+        <v>88594</v>
       </c>
       <c r="W62">
-        <v>24.9286</v>
+        <v>14.0794</v>
       </c>
     </row>
     <row r="63" spans="1:23">
@@ -5075,64 +5054,64 @@
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F63">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="G63" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H63">
-        <v>30.290503</v>
+        <v>30.4426709</v>
       </c>
       <c r="I63">
-        <v>74.220803</v>
+        <v>74.4101264</v>
       </c>
       <c r="J63">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K63">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L63">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M63" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N63">
-        <v>401</v>
+        <v>870</v>
       </c>
       <c r="O63" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
       </c>
       <c r="Q63" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="R63" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="S63">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T63">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U63" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V63">
-        <v>43110</v>
+        <v>10000</v>
       </c>
       <c r="W63">
-        <v>20.8569</v>
+        <v>14.0794</v>
       </c>
     </row>
     <row r="64" spans="1:23">
@@ -5149,46 +5128,46 @@
         <v>29</v>
       </c>
       <c r="E64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F64">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H64">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I64">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J64">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K64">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L64">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M64" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N64">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="O64" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
       </c>
       <c r="Q64" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S64">
         <v>30.458388</v>
@@ -5197,13 +5176,13 @@
         <v>74.453514</v>
       </c>
       <c r="U64" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V64">
-        <v>197630</v>
+        <v>5000</v>
       </c>
       <c r="W64">
-        <v>152.8348</v>
+        <v>14.0794</v>
       </c>
     </row>
     <row r="65" spans="1:23">
@@ -5220,46 +5199,46 @@
         <v>29</v>
       </c>
       <c r="E65" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F65">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G65" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="H65">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I65">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J65">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K65">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L65">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M65" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N65">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="O65" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
       </c>
       <c r="Q65" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R65" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S65">
         <v>30.458388</v>
@@ -5268,13 +5247,13 @@
         <v>74.453514</v>
       </c>
       <c r="U65" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V65">
-        <v>16680</v>
+        <v>5000</v>
       </c>
       <c r="W65">
-        <v>152.8348</v>
+        <v>14.0794</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -5291,46 +5270,46 @@
         <v>29</v>
       </c>
       <c r="E66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F66">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G66" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H66">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I66">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J66">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K66">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L66">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M66" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N66">
         <v>866</v>
       </c>
       <c r="O66" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
       </c>
       <c r="Q66" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R66" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S66">
         <v>30.458388</v>
@@ -5339,13 +5318,13 @@
         <v>74.453514</v>
       </c>
       <c r="U66" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V66">
-        <v>42630</v>
+        <v>38086</v>
       </c>
       <c r="W66">
-        <v>152.8348</v>
+        <v>10.1617</v>
       </c>
     </row>
     <row r="67" spans="1:23">
@@ -5362,46 +5341,46 @@
         <v>29</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F67">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H67">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I67">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J67">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K67">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L67">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M67" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N67">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="O67" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
       </c>
       <c r="Q67" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R67" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S67">
         <v>30.458388</v>
@@ -5410,13 +5389,13 @@
         <v>74.453514</v>
       </c>
       <c r="U67" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V67">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W67">
-        <v>152.8348</v>
+        <v>10.1617</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -5433,46 +5412,46 @@
         <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F68">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="H68">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I68">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J68">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K68">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L68">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M68" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N68">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="O68" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
       </c>
       <c r="Q68" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R68" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S68">
         <v>30.458388</v>
@@ -5481,13 +5460,13 @@
         <v>74.453514</v>
       </c>
       <c r="U68" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V68">
-        <v>10000</v>
+        <v>5127</v>
       </c>
       <c r="W68">
-        <v>152.8348</v>
+        <v>10.1617</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5504,46 +5483,46 @@
         <v>29</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F69">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H69">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I69">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J69">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K69">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L69">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M69" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N69">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="O69" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
       </c>
       <c r="Q69" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R69" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S69">
         <v>30.458388</v>
@@ -5552,13 +5531,13 @@
         <v>74.453514</v>
       </c>
       <c r="U69" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V69">
-        <v>10000</v>
+        <v>294680</v>
       </c>
       <c r="W69">
-        <v>152.8348</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="70" spans="1:23">
@@ -5575,46 +5554,46 @@
         <v>29</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F70">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G70" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H70">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I70">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J70">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K70">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L70">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M70" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N70">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="O70" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
       </c>
       <c r="Q70" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R70" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S70">
         <v>30.458388</v>
@@ -5623,13 +5602,13 @@
         <v>74.453514</v>
       </c>
       <c r="U70" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V70">
-        <v>30720</v>
+        <v>16680</v>
       </c>
       <c r="W70">
-        <v>152.8348</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="71" spans="1:23">
@@ -5646,46 +5625,46 @@
         <v>29</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F71">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H71">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I71">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J71">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K71">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L71">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M71" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N71">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="O71" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
       </c>
       <c r="Q71" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S71">
         <v>30.458388</v>
@@ -5694,13 +5673,13 @@
         <v>74.453514</v>
       </c>
       <c r="U71" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V71">
-        <v>1080</v>
+        <v>10000</v>
       </c>
       <c r="W71">
-        <v>152.8348</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="72" spans="1:23">
@@ -5717,46 +5696,46 @@
         <v>29</v>
       </c>
       <c r="E72" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F72">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H72">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I72">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J72">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K72">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L72">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M72" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N72">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="O72" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
       </c>
       <c r="Q72" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R72" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S72">
         <v>30.458388</v>
@@ -5765,13 +5744,13 @@
         <v>74.453514</v>
       </c>
       <c r="U72" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V72">
-        <v>29640</v>
+        <v>10000</v>
       </c>
       <c r="W72">
-        <v>152.8348</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="73" spans="1:23">
@@ -5788,46 +5767,46 @@
         <v>29</v>
       </c>
       <c r="E73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F73">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H73">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I73">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J73">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K73">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L73">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M73" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N73">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="O73" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
       </c>
       <c r="Q73" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R73" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S73">
         <v>30.458388</v>
@@ -5836,13 +5815,13 @@
         <v>74.453514</v>
       </c>
       <c r="U73" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V73">
-        <v>9950</v>
+        <v>10000</v>
       </c>
       <c r="W73">
-        <v>152.8348</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="74" spans="1:23">
@@ -5859,46 +5838,46 @@
         <v>29</v>
       </c>
       <c r="E74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F74">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G74" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H74">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I74">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J74">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K74">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L74">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M74" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N74">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="O74" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
       </c>
       <c r="Q74" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R74" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S74">
         <v>30.458388</v>
@@ -5907,13 +5886,13 @@
         <v>74.453514</v>
       </c>
       <c r="U74" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V74">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W74">
-        <v>153.406</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="75" spans="1:23">
@@ -5930,46 +5909,46 @@
         <v>29</v>
       </c>
       <c r="E75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F75">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G75" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H75">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I75">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J75">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K75">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L75">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M75" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N75">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="O75" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
       </c>
       <c r="Q75" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R75" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S75">
         <v>30.458388</v>
@@ -5978,13 +5957,13 @@
         <v>74.453514</v>
       </c>
       <c r="U75" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V75">
-        <v>5000</v>
+        <v>29640</v>
       </c>
       <c r="W75">
-        <v>153.406</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -6001,46 +5980,46 @@
         <v>29</v>
       </c>
       <c r="E76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F76">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G76" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H76">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I76">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J76">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K76">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L76">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M76" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N76">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="O76" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
       </c>
       <c r="Q76" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R76" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S76">
         <v>30.458388</v>
@@ -6049,13 +6028,13 @@
         <v>74.453514</v>
       </c>
       <c r="U76" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V76">
-        <v>5000</v>
+        <v>28460</v>
       </c>
       <c r="W76">
-        <v>153.406</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="77" spans="1:23">
@@ -6072,46 +6051,46 @@
         <v>29</v>
       </c>
       <c r="E77" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F77">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G77" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H77">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I77">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J77">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K77">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L77">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M77" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N77">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O77" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
       </c>
       <c r="Q77" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R77" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S77">
         <v>30.458388</v>
@@ -6120,13 +6099,13 @@
         <v>74.453514</v>
       </c>
       <c r="U77" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V77">
-        <v>20480</v>
+        <v>15353</v>
       </c>
       <c r="W77">
-        <v>153.406</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -6143,46 +6122,46 @@
         <v>29</v>
       </c>
       <c r="E78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F78">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G78" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H78">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I78">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J78">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K78">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L78">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M78" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N78">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O78" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
       </c>
       <c r="Q78" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R78" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S78">
         <v>30.458388</v>
@@ -6191,13 +6170,13 @@
         <v>74.453514</v>
       </c>
       <c r="U78" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V78">
-        <v>18000</v>
+        <v>20480</v>
       </c>
       <c r="W78">
-        <v>153.406</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -6214,46 +6193,46 @@
         <v>29</v>
       </c>
       <c r="E79" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F79">
-        <v>1324</v>
+        <v>1607</v>
       </c>
       <c r="G79" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H79">
-        <v>30.59296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I79">
-        <v>75.78903</v>
+        <v>74.5049465</v>
       </c>
       <c r="J79">
-        <v>216</v>
+        <v>1512</v>
       </c>
       <c r="K79">
-        <v>30.5076194</v>
+        <v>30.4713293</v>
       </c>
       <c r="L79">
-        <v>74.958715</v>
+        <v>74.5033904</v>
       </c>
       <c r="M79" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N79">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="O79" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
       </c>
       <c r="Q79" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R79" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S79">
         <v>30.458388</v>
@@ -6262,13 +6241,13 @@
         <v>74.453514</v>
       </c>
       <c r="U79" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V79">
-        <v>41830</v>
+        <v>20480</v>
       </c>
       <c r="W79">
-        <v>159.8987</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="80" spans="1:23">
@@ -6285,46 +6264,46 @@
         <v>29</v>
       </c>
       <c r="E80" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F80">
-        <v>1325</v>
+        <v>1607</v>
       </c>
       <c r="G80" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H80">
-        <v>30.61907</v>
+        <v>30.4726737</v>
       </c>
       <c r="I80">
-        <v>75.8098</v>
+        <v>74.5049465</v>
       </c>
       <c r="J80">
-        <v>217</v>
+        <v>1512</v>
       </c>
       <c r="K80">
-        <v>30.51445</v>
+        <v>30.4713293</v>
       </c>
       <c r="L80">
-        <v>74.89836</v>
+        <v>74.5033904</v>
       </c>
       <c r="M80" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N80">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="O80" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
       </c>
       <c r="Q80" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="R80" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S80">
         <v>30.458388</v>
@@ -6333,13 +6312,13 @@
         <v>74.453514</v>
       </c>
       <c r="U80" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V80">
-        <v>55220</v>
+        <v>15360</v>
       </c>
       <c r="W80">
-        <v>195.7033</v>
+        <v>5.3025</v>
       </c>
     </row>
     <row r="81" spans="1:23">
@@ -6356,61 +6335,61 @@
         <v>29</v>
       </c>
       <c r="E81" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F81">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G81" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H81">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I81">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J81">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K81">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L81">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M81" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N81">
-        <v>866</v>
+        <v>401</v>
       </c>
       <c r="O81" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P81" t="s">
         <v>25</v>
       </c>
       <c r="Q81" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R81" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S81">
-        <v>30.458388</v>
+        <v>30.17081207</v>
       </c>
       <c r="T81">
-        <v>74.453514</v>
+        <v>74.18179719</v>
       </c>
       <c r="U81" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V81">
-        <v>13140</v>
+        <v>1314.5</v>
       </c>
       <c r="W81">
-        <v>183.9833</v>
+        <v>23.7515</v>
       </c>
     </row>
     <row r="82" spans="1:23">
@@ -6427,61 +6406,61 @@
         <v>29</v>
       </c>
       <c r="E82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F82">
-        <v>1326</v>
+        <v>1660</v>
       </c>
       <c r="G82" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H82">
-        <v>30.60582</v>
+        <v>30.2397029</v>
       </c>
       <c r="I82">
-        <v>75.87558</v>
+        <v>74.2953411</v>
       </c>
       <c r="J82">
-        <v>57</v>
+        <v>279</v>
       </c>
       <c r="K82">
-        <v>30.58822</v>
+        <v>30.175344</v>
       </c>
       <c r="L82">
-        <v>75.6722</v>
+        <v>74.178363</v>
       </c>
       <c r="M82" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N82">
-        <v>874</v>
+        <v>406</v>
       </c>
       <c r="O82" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P82" t="s">
         <v>25</v>
       </c>
       <c r="Q82" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="R82" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S82">
-        <v>30.458388</v>
+        <v>30.16991135</v>
       </c>
       <c r="T82">
-        <v>74.453514</v>
+        <v>74.18230296</v>
       </c>
       <c r="U82" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V82">
-        <v>28460</v>
+        <v>52394.5</v>
       </c>
       <c r="W82">
-        <v>183.9833</v>
+        <v>23.8639</v>
       </c>
     </row>
     <row r="83" spans="1:23">
@@ -6495,64 +6474,64 @@
         <v>25</v>
       </c>
       <c r="D83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F83">
-        <v>1326</v>
+        <v>2153</v>
       </c>
       <c r="G83" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H83">
-        <v>30.60582</v>
+        <v>31.3953454</v>
       </c>
       <c r="I83">
-        <v>75.87558</v>
+        <v>74.6222925</v>
       </c>
       <c r="J83">
-        <v>57</v>
+        <v>1948</v>
       </c>
       <c r="K83">
-        <v>30.58822</v>
+        <v>31.361236</v>
       </c>
       <c r="L83">
-        <v>75.6722</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M83" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N83">
-        <v>879</v>
+        <v>2</v>
       </c>
       <c r="O83" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P83" t="s">
         <v>25</v>
       </c>
       <c r="Q83" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R83" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S83">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T83">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U83" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V83">
-        <v>2480</v>
+        <v>150000</v>
       </c>
       <c r="W83">
-        <v>183.9833</v>
+        <v>61.349</v>
       </c>
     </row>
     <row r="84" spans="1:23">
@@ -6566,419 +6545,64 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F84">
-        <v>1327</v>
+        <v>2153</v>
       </c>
       <c r="G84" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H84">
-        <v>30.62411</v>
+        <v>31.3953454</v>
       </c>
       <c r="I84">
-        <v>75.75073</v>
+        <v>74.6222925</v>
       </c>
       <c r="J84">
-        <v>217</v>
+        <v>1948</v>
       </c>
       <c r="K84">
-        <v>30.51445</v>
+        <v>31.361236</v>
       </c>
       <c r="L84">
-        <v>74.89836</v>
+        <v>74.66727400000001</v>
       </c>
       <c r="M84" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="N84">
-        <v>866</v>
+        <v>4</v>
       </c>
       <c r="O84" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P84" t="s">
         <v>25</v>
       </c>
       <c r="Q84" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="R84" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="S84">
-        <v>30.458388</v>
+        <v>31.45335</v>
       </c>
       <c r="T84">
-        <v>74.453514</v>
+        <v>74.46541999999999</v>
       </c>
       <c r="U84" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="V84">
-        <v>59240</v>
+        <v>150000</v>
       </c>
       <c r="W84">
-        <v>189.9006</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23">
-      <c r="A85" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" t="s">
-        <v>33</v>
-      </c>
-      <c r="F85">
-        <v>1328</v>
-      </c>
-      <c r="G85" t="s">
-        <v>89</v>
-      </c>
-      <c r="H85">
-        <v>30.58776</v>
-      </c>
-      <c r="I85">
-        <v>75.81787</v>
-      </c>
-      <c r="J85">
-        <v>216</v>
-      </c>
-      <c r="K85">
-        <v>30.5076194</v>
-      </c>
-      <c r="L85">
-        <v>74.958715</v>
-      </c>
-      <c r="M85" t="s">
-        <v>93</v>
-      </c>
-      <c r="N85">
-        <v>866</v>
-      </c>
-      <c r="O85" t="s">
-        <v>94</v>
-      </c>
-      <c r="P85" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>29</v>
-      </c>
-      <c r="R85" t="s">
-        <v>33</v>
-      </c>
-      <c r="S85">
-        <v>30.458388</v>
-      </c>
-      <c r="T85">
-        <v>74.453514</v>
-      </c>
-      <c r="U85" t="s">
-        <v>95</v>
-      </c>
-      <c r="V85">
-        <v>11670</v>
-      </c>
-      <c r="W85">
-        <v>161.3797</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23">
-      <c r="A86" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" t="s">
-        <v>29</v>
-      </c>
-      <c r="E86" t="s">
-        <v>33</v>
-      </c>
-      <c r="F86">
-        <v>1328</v>
-      </c>
-      <c r="G86" t="s">
-        <v>89</v>
-      </c>
-      <c r="H86">
-        <v>30.58776</v>
-      </c>
-      <c r="I86">
-        <v>75.81787</v>
-      </c>
-      <c r="J86">
-        <v>216</v>
-      </c>
-      <c r="K86">
-        <v>30.5076194</v>
-      </c>
-      <c r="L86">
-        <v>74.958715</v>
-      </c>
-      <c r="M86" t="s">
-        <v>93</v>
-      </c>
-      <c r="N86">
-        <v>880</v>
-      </c>
-      <c r="O86" t="s">
-        <v>94</v>
-      </c>
-      <c r="P86" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>29</v>
-      </c>
-      <c r="R86" t="s">
-        <v>33</v>
-      </c>
-      <c r="S86">
-        <v>30.458388</v>
-      </c>
-      <c r="T86">
-        <v>74.453514</v>
-      </c>
-      <c r="U86" t="s">
-        <v>95</v>
-      </c>
-      <c r="V86">
-        <v>15360</v>
-      </c>
-      <c r="W86">
-        <v>161.3797</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23">
-      <c r="A87" t="s">
-        <v>23</v>
-      </c>
-      <c r="B87" t="s">
-        <v>24</v>
-      </c>
-      <c r="C87" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" t="s">
-        <v>29</v>
-      </c>
-      <c r="E87" t="s">
-        <v>33</v>
-      </c>
-      <c r="F87">
-        <v>1329</v>
-      </c>
-      <c r="G87" t="s">
-        <v>90</v>
-      </c>
-      <c r="H87">
-        <v>30.669134</v>
-      </c>
-      <c r="I87">
-        <v>75.877723</v>
-      </c>
-      <c r="J87">
-        <v>678</v>
-      </c>
-      <c r="K87">
-        <v>30.633572</v>
-      </c>
-      <c r="L87">
-        <v>75.628421</v>
-      </c>
-      <c r="M87" t="s">
-        <v>93</v>
-      </c>
-      <c r="N87">
-        <v>877</v>
-      </c>
-      <c r="O87" t="s">
-        <v>94</v>
-      </c>
-      <c r="P87" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>29</v>
-      </c>
-      <c r="R87" t="s">
-        <v>33</v>
-      </c>
-      <c r="S87">
-        <v>30.458388</v>
-      </c>
-      <c r="T87">
-        <v>74.453514</v>
-      </c>
-      <c r="U87" t="s">
-        <v>95</v>
-      </c>
-      <c r="V87">
-        <v>10530</v>
-      </c>
-      <c r="W87">
-        <v>172.9693</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23">
-      <c r="A88" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" t="s">
-        <v>24</v>
-      </c>
-      <c r="C88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s">
-        <v>29</v>
-      </c>
-      <c r="E88" t="s">
-        <v>33</v>
-      </c>
-      <c r="F88">
-        <v>1330</v>
-      </c>
-      <c r="G88" t="s">
-        <v>91</v>
-      </c>
-      <c r="H88">
-        <v>30.651445</v>
-      </c>
-      <c r="I88">
-        <v>75.890028</v>
-      </c>
-      <c r="J88">
-        <v>1225</v>
-      </c>
-      <c r="K88">
-        <v>30.5792101</v>
-      </c>
-      <c r="L88">
-        <v>75.30097960000001</v>
-      </c>
-      <c r="M88" t="s">
-        <v>93</v>
-      </c>
-      <c r="N88">
-        <v>872</v>
-      </c>
-      <c r="O88" t="s">
-        <v>94</v>
-      </c>
-      <c r="P88" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>29</v>
-      </c>
-      <c r="R88" t="s">
-        <v>33</v>
-      </c>
-      <c r="S88">
-        <v>30.458388</v>
-      </c>
-      <c r="T88">
-        <v>74.453514</v>
-      </c>
-      <c r="U88" t="s">
-        <v>95</v>
-      </c>
-      <c r="V88">
-        <v>29640</v>
-      </c>
-      <c r="W88">
-        <v>159.9022</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23">
-      <c r="A89" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" t="s">
-        <v>24</v>
-      </c>
-      <c r="C89" t="s">
-        <v>26</v>
-      </c>
-      <c r="D89" t="s">
-        <v>30</v>
-      </c>
-      <c r="E89" t="s">
-        <v>34</v>
-      </c>
-      <c r="F89">
-        <v>1660</v>
-      </c>
-      <c r="G89" t="s">
-        <v>92</v>
-      </c>
-      <c r="H89">
-        <v>30.2397029</v>
-      </c>
-      <c r="I89">
-        <v>74.2953411</v>
-      </c>
-      <c r="J89">
-        <v>287</v>
-      </c>
-      <c r="K89">
-        <v>30.126927</v>
-      </c>
-      <c r="L89">
-        <v>74.161942</v>
-      </c>
-      <c r="M89" t="s">
-        <v>93</v>
-      </c>
-      <c r="N89">
-        <v>407</v>
-      </c>
-      <c r="O89" t="s">
-        <v>94</v>
-      </c>
-      <c r="P89" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>28</v>
-      </c>
-      <c r="R89" t="s">
-        <v>32</v>
-      </c>
-      <c r="S89">
-        <v>30.126927</v>
-      </c>
-      <c r="T89">
-        <v>74.161942</v>
-      </c>
-      <c r="U89" t="s">
-        <v>95</v>
-      </c>
-      <c r="V89">
-        <v>15621</v>
-      </c>
-      <c r="W89">
-        <v>25.2685</v>
+        <v>61.349</v>
       </c>
     </row>
   </sheetData>

--- a/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="92">
   <si>
     <t>Scenario</t>
   </si>
@@ -277,7 +277,16 @@
     <t>agah</t>
   </si>
   <si>
-    <t>MALERKOTLA</t>
+    <t>Amritsar</t>
+  </si>
+  <si>
+    <t>Fazilka</t>
+  </si>
+  <si>
+    <t>Jalandhar</t>
+  </si>
+  <si>
+    <t>Malerkotla</t>
   </si>
   <si>
     <t>Paddy</t>
@@ -762,7 +771,7 @@
         <v>25</v>
       </c>
       <c r="Q2" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="R2" t="s">
         <v>31</v>
@@ -774,7 +783,7 @@
         <v>74.91584450000001</v>
       </c>
       <c r="U2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V2">
         <v>50000</v>
@@ -833,7 +842,7 @@
         <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="R3" t="s">
         <v>31</v>
@@ -845,7 +854,7 @@
         <v>74.588493</v>
       </c>
       <c r="U3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V3">
         <v>50000</v>
@@ -904,7 +913,7 @@
         <v>25</v>
       </c>
       <c r="Q4" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R4" t="s">
         <v>31</v>
@@ -916,7 +925,7 @@
         <v>74.18214294000001</v>
       </c>
       <c r="U4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V4">
         <v>90000</v>
@@ -975,7 +984,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R5" t="s">
         <v>31</v>
@@ -987,7 +996,7 @@
         <v>74.18094151</v>
       </c>
       <c r="U5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V5">
         <v>60000</v>
@@ -1046,7 +1055,7 @@
         <v>25</v>
       </c>
       <c r="Q6" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R6" t="s">
         <v>31</v>
@@ -1058,7 +1067,7 @@
         <v>74.18085842000001</v>
       </c>
       <c r="U6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V6">
         <v>120000</v>
@@ -1117,7 +1126,7 @@
         <v>25</v>
       </c>
       <c r="Q7" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R7" t="s">
         <v>31</v>
@@ -1129,7 +1138,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V7">
         <v>33610</v>
@@ -1188,7 +1197,7 @@
         <v>25</v>
       </c>
       <c r="Q8" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R8" t="s">
         <v>31</v>
@@ -1200,7 +1209,7 @@
         <v>74.18315728</v>
       </c>
       <c r="U8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V8">
         <v>150000</v>
@@ -1259,7 +1268,7 @@
         <v>25</v>
       </c>
       <c r="Q9" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R9" t="s">
         <v>31</v>
@@ -1271,7 +1280,7 @@
         <v>74.161942</v>
       </c>
       <c r="U9" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V9">
         <v>143264</v>
@@ -1330,7 +1339,7 @@
         <v>25</v>
       </c>
       <c r="Q10" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R10" t="s">
         <v>31</v>
@@ -1342,7 +1351,7 @@
         <v>74.20908439</v>
       </c>
       <c r="U10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V10">
         <v>48247.5</v>
@@ -1401,7 +1410,7 @@
         <v>25</v>
       </c>
       <c r="Q11" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R11" t="s">
         <v>31</v>
@@ -1413,7 +1422,7 @@
         <v>74.206666</v>
       </c>
       <c r="U11" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V11">
         <v>23588</v>
@@ -1472,7 +1481,7 @@
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R12" t="s">
         <v>31</v>
@@ -1484,7 +1493,7 @@
         <v>74.18014506</v>
       </c>
       <c r="U12" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V12">
         <v>73860.5</v>
@@ -1543,7 +1552,7 @@
         <v>25</v>
       </c>
       <c r="Q13" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R13" t="s">
         <v>31</v>
@@ -1555,7 +1564,7 @@
         <v>74.161942</v>
       </c>
       <c r="U13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V13">
         <v>37309</v>
@@ -1614,7 +1623,7 @@
         <v>25</v>
       </c>
       <c r="Q14" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R14" t="s">
         <v>31</v>
@@ -1626,7 +1635,7 @@
         <v>74.161942</v>
       </c>
       <c r="U14" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V14">
         <v>18025.5</v>
@@ -1685,7 +1694,7 @@
         <v>25</v>
       </c>
       <c r="Q15" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R15" t="s">
         <v>31</v>
@@ -1697,7 +1706,7 @@
         <v>74.20908439</v>
       </c>
       <c r="U15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V15">
         <v>16177.5</v>
@@ -1756,7 +1765,7 @@
         <v>25</v>
       </c>
       <c r="Q16" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R16" t="s">
         <v>31</v>
@@ -1768,7 +1777,7 @@
         <v>74.20888524</v>
       </c>
       <c r="U16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V16">
         <v>33588.5</v>
@@ -1827,7 +1836,7 @@
         <v>25</v>
       </c>
       <c r="Q17" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R17" t="s">
         <v>31</v>
@@ -1839,7 +1848,7 @@
         <v>74.183232</v>
       </c>
       <c r="U17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V17">
         <v>13129</v>
@@ -1898,7 +1907,7 @@
         <v>25</v>
       </c>
       <c r="Q18" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R18" t="s">
         <v>31</v>
@@ -1910,7 +1919,7 @@
         <v>74.161942</v>
       </c>
       <c r="U18" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V18">
         <v>28578.5</v>
@@ -1969,7 +1978,7 @@
         <v>25</v>
       </c>
       <c r="Q19" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R19" t="s">
         <v>31</v>
@@ -1981,7 +1990,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V19">
         <v>18038</v>
@@ -2040,7 +2049,7 @@
         <v>25</v>
       </c>
       <c r="Q20" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R20" t="s">
         <v>31</v>
@@ -2052,7 +2061,7 @@
         <v>74.161942</v>
       </c>
       <c r="U20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V20">
         <v>44568.5</v>
@@ -2111,7 +2120,7 @@
         <v>25</v>
       </c>
       <c r="Q21" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R21" t="s">
         <v>31</v>
@@ -2123,7 +2132,7 @@
         <v>74.206666</v>
       </c>
       <c r="U21" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V21">
         <v>25216</v>
@@ -2182,7 +2191,7 @@
         <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R22" t="s">
         <v>31</v>
@@ -2194,7 +2203,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V22">
         <v>44802</v>
@@ -2253,7 +2262,7 @@
         <v>25</v>
       </c>
       <c r="Q23" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R23" t="s">
         <v>31</v>
@@ -2265,7 +2274,7 @@
         <v>74.161942</v>
       </c>
       <c r="U23" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V23">
         <v>30276.5</v>
@@ -2324,7 +2333,7 @@
         <v>25</v>
       </c>
       <c r="Q24" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R24" t="s">
         <v>31</v>
@@ -2336,7 +2345,7 @@
         <v>74.20888524</v>
       </c>
       <c r="U24" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V24">
         <v>19961.5</v>
@@ -2395,7 +2404,7 @@
         <v>25</v>
       </c>
       <c r="Q25" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R25" t="s">
         <v>31</v>
@@ -2407,7 +2416,7 @@
         <v>74.20908439</v>
       </c>
       <c r="U25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V25">
         <v>64381</v>
@@ -2466,7 +2475,7 @@
         <v>25</v>
       </c>
       <c r="Q26" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R26" t="s">
         <v>31</v>
@@ -2478,7 +2487,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U26" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V26">
         <v>39817.5</v>
@@ -2537,7 +2546,7 @@
         <v>25</v>
       </c>
       <c r="Q27" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R27" t="s">
         <v>31</v>
@@ -2549,7 +2558,7 @@
         <v>74.183232</v>
       </c>
       <c r="U27" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V27">
         <v>10375.5</v>
@@ -2608,7 +2617,7 @@
         <v>25</v>
       </c>
       <c r="Q28" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R28" t="s">
         <v>31</v>
@@ -2620,7 +2629,7 @@
         <v>74.161942</v>
       </c>
       <c r="U28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V28">
         <v>100949.5</v>
@@ -2679,7 +2688,7 @@
         <v>25</v>
       </c>
       <c r="Q29" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R29" t="s">
         <v>31</v>
@@ -2691,7 +2700,7 @@
         <v>74.17723581</v>
       </c>
       <c r="U29" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V29">
         <v>36622.5</v>
@@ -2750,7 +2759,7 @@
         <v>25</v>
       </c>
       <c r="Q30" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R30" t="s">
         <v>31</v>
@@ -2762,7 +2771,7 @@
         <v>74.18014506</v>
       </c>
       <c r="U30" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V30">
         <v>11652.5</v>
@@ -2821,7 +2830,7 @@
         <v>25</v>
       </c>
       <c r="Q31" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R31" t="s">
         <v>31</v>
@@ -2833,7 +2842,7 @@
         <v>74.161942</v>
       </c>
       <c r="U31" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V31">
         <v>16592.5</v>
@@ -2892,7 +2901,7 @@
         <v>25</v>
       </c>
       <c r="Q32" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R32" t="s">
         <v>31</v>
@@ -2904,7 +2913,7 @@
         <v>74.161942</v>
       </c>
       <c r="U32" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V32">
         <v>21311</v>
@@ -2963,7 +2972,7 @@
         <v>25</v>
       </c>
       <c r="Q33" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R33" t="s">
         <v>31</v>
@@ -2975,7 +2984,7 @@
         <v>74.20908439</v>
       </c>
       <c r="U33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V33">
         <v>34094</v>
@@ -3034,7 +3043,7 @@
         <v>25</v>
       </c>
       <c r="Q34" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R34" t="s">
         <v>31</v>
@@ -3046,7 +3055,7 @@
         <v>74.183232</v>
       </c>
       <c r="U34" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V34">
         <v>10795.5</v>
@@ -3105,7 +3114,7 @@
         <v>25</v>
       </c>
       <c r="Q35" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R35" t="s">
         <v>31</v>
@@ -3117,7 +3126,7 @@
         <v>74.18230296</v>
       </c>
       <c r="U35" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V35">
         <v>21605.5</v>
@@ -3176,7 +3185,7 @@
         <v>25</v>
       </c>
       <c r="Q36" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R36" t="s">
         <v>31</v>
@@ -3188,7 +3197,7 @@
         <v>74.206666</v>
       </c>
       <c r="U36" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V36">
         <v>71196</v>
@@ -3247,7 +3256,7 @@
         <v>25</v>
       </c>
       <c r="Q37" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R37" t="s">
         <v>31</v>
@@ -3259,7 +3268,7 @@
         <v>74.161942</v>
       </c>
       <c r="U37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V37">
         <v>2489</v>
@@ -3318,7 +3327,7 @@
         <v>25</v>
       </c>
       <c r="Q38" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R38" t="s">
         <v>31</v>
@@ -3330,7 +3339,7 @@
         <v>74.161942</v>
       </c>
       <c r="U38" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V38">
         <v>34208</v>
@@ -3389,7 +3398,7 @@
         <v>25</v>
       </c>
       <c r="Q39" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R39" t="s">
         <v>31</v>
@@ -3401,7 +3410,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U39" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V39">
         <v>54819.5</v>
@@ -3460,7 +3469,7 @@
         <v>25</v>
       </c>
       <c r="Q40" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R40" t="s">
         <v>31</v>
@@ -3472,7 +3481,7 @@
         <v>74.161942</v>
       </c>
       <c r="U40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V40">
         <v>37768</v>
@@ -3531,7 +3540,7 @@
         <v>25</v>
       </c>
       <c r="Q41" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R41" t="s">
         <v>31</v>
@@ -3543,7 +3552,7 @@
         <v>74.161942</v>
       </c>
       <c r="U41" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V41">
         <v>29874.5</v>
@@ -3602,7 +3611,7 @@
         <v>25</v>
       </c>
       <c r="Q42" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R42" t="s">
         <v>31</v>
@@ -3614,7 +3623,7 @@
         <v>74.161942</v>
       </c>
       <c r="U42" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V42">
         <v>56983.5</v>
@@ -3673,7 +3682,7 @@
         <v>25</v>
       </c>
       <c r="Q43" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R43" t="s">
         <v>31</v>
@@ -3685,7 +3694,7 @@
         <v>74.161942</v>
       </c>
       <c r="U43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V43">
         <v>23195.5</v>
@@ -3744,7 +3753,7 @@
         <v>25</v>
       </c>
       <c r="Q44" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R44" t="s">
         <v>31</v>
@@ -3756,7 +3765,7 @@
         <v>74.161942</v>
       </c>
       <c r="U44" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V44">
         <v>57368</v>
@@ -3815,7 +3824,7 @@
         <v>25</v>
       </c>
       <c r="Q45" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R45" t="s">
         <v>31</v>
@@ -3827,7 +3836,7 @@
         <v>74.18014506</v>
       </c>
       <c r="U45" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V45">
         <v>2487</v>
@@ -3886,7 +3895,7 @@
         <v>25</v>
       </c>
       <c r="Q46" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R46" t="s">
         <v>31</v>
@@ -3898,7 +3907,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U46" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V46">
         <v>29195</v>
@@ -3957,7 +3966,7 @@
         <v>25</v>
       </c>
       <c r="Q47" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R47" t="s">
         <v>31</v>
@@ -3969,7 +3978,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U47" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V47">
         <v>26795</v>
@@ -4028,7 +4037,7 @@
         <v>25</v>
       </c>
       <c r="Q48" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R48" t="s">
         <v>31</v>
@@ -4040,7 +4049,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U48" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V48">
         <v>7950</v>
@@ -4099,7 +4108,7 @@
         <v>25</v>
       </c>
       <c r="Q49" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R49" t="s">
         <v>31</v>
@@ -4111,7 +4120,7 @@
         <v>74.18014506</v>
       </c>
       <c r="U49" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V49">
         <v>5500</v>
@@ -4170,7 +4179,7 @@
         <v>25</v>
       </c>
       <c r="Q50" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R50" t="s">
         <v>31</v>
@@ -4182,7 +4191,7 @@
         <v>74.161942</v>
       </c>
       <c r="U50" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V50">
         <v>12630.5</v>
@@ -4241,7 +4250,7 @@
         <v>25</v>
       </c>
       <c r="Q51" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R51" t="s">
         <v>31</v>
@@ -4253,7 +4262,7 @@
         <v>74.161942</v>
       </c>
       <c r="U51" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V51">
         <v>13803</v>
@@ -4312,7 +4321,7 @@
         <v>25</v>
       </c>
       <c r="Q52" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R52" t="s">
         <v>31</v>
@@ -4324,7 +4333,7 @@
         <v>74.161942</v>
       </c>
       <c r="U52" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V52">
         <v>9145</v>
@@ -4383,7 +4392,7 @@
         <v>25</v>
       </c>
       <c r="Q53" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R53" t="s">
         <v>31</v>
@@ -4395,7 +4404,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U53" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V53">
         <v>17622.5</v>
@@ -4454,7 +4463,7 @@
         <v>25</v>
       </c>
       <c r="Q54" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R54" t="s">
         <v>31</v>
@@ -4466,7 +4475,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U54" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V54">
         <v>2347.5</v>
@@ -4525,7 +4534,7 @@
         <v>25</v>
       </c>
       <c r="Q55" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R55" t="s">
         <v>31</v>
@@ -4537,7 +4546,7 @@
         <v>74.17723581</v>
       </c>
       <c r="U55" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V55">
         <v>40337.5</v>
@@ -4596,7 +4605,7 @@
         <v>25</v>
       </c>
       <c r="Q56" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R56" t="s">
         <v>31</v>
@@ -4608,7 +4617,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U56" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V56">
         <v>56502.5</v>
@@ -4667,7 +4676,7 @@
         <v>25</v>
       </c>
       <c r="Q57" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R57" t="s">
         <v>31</v>
@@ -4679,7 +4688,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U57" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V57">
         <v>43110</v>
@@ -4738,7 +4747,7 @@
         <v>25</v>
       </c>
       <c r="Q58" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R58" t="s">
         <v>31</v>
@@ -4750,7 +4759,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U58" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V58">
         <v>128218</v>
@@ -4809,7 +4818,7 @@
         <v>25</v>
       </c>
       <c r="Q59" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R59" t="s">
         <v>31</v>
@@ -4821,7 +4830,7 @@
         <v>74.16401603</v>
       </c>
       <c r="U59" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V59">
         <v>62709.5</v>
@@ -4880,7 +4889,7 @@
         <v>25</v>
       </c>
       <c r="Q60" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R60" t="s">
         <v>31</v>
@@ -4892,7 +4901,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U60" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V60">
         <v>47189.5</v>
@@ -4951,7 +4960,7 @@
         <v>25</v>
       </c>
       <c r="Q61" t="s">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="R61" t="s">
         <v>31</v>
@@ -4963,7 +4972,7 @@
         <v>75.685958</v>
       </c>
       <c r="U61" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V61">
         <v>21500</v>
@@ -5022,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="Q62" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R62" t="s">
         <v>31</v>
@@ -5034,7 +5043,7 @@
         <v>74.453514</v>
       </c>
       <c r="U62" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V62">
         <v>88594</v>
@@ -5093,7 +5102,7 @@
         <v>25</v>
       </c>
       <c r="Q63" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R63" t="s">
         <v>31</v>
@@ -5105,7 +5114,7 @@
         <v>74.453514</v>
       </c>
       <c r="U63" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V63">
         <v>10000</v>
@@ -5164,7 +5173,7 @@
         <v>25</v>
       </c>
       <c r="Q64" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R64" t="s">
         <v>31</v>
@@ -5176,7 +5185,7 @@
         <v>74.453514</v>
       </c>
       <c r="U64" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V64">
         <v>5000</v>
@@ -5235,7 +5244,7 @@
         <v>25</v>
       </c>
       <c r="Q65" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R65" t="s">
         <v>31</v>
@@ -5247,7 +5256,7 @@
         <v>74.453514</v>
       </c>
       <c r="U65" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V65">
         <v>5000</v>
@@ -5306,7 +5315,7 @@
         <v>25</v>
       </c>
       <c r="Q66" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R66" t="s">
         <v>31</v>
@@ -5318,7 +5327,7 @@
         <v>74.453514</v>
       </c>
       <c r="U66" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V66">
         <v>38086</v>
@@ -5377,7 +5386,7 @@
         <v>25</v>
       </c>
       <c r="Q67" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R67" t="s">
         <v>31</v>
@@ -5389,7 +5398,7 @@
         <v>74.453514</v>
       </c>
       <c r="U67" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V67">
         <v>30720</v>
@@ -5448,7 +5457,7 @@
         <v>25</v>
       </c>
       <c r="Q68" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R68" t="s">
         <v>31</v>
@@ -5460,7 +5469,7 @@
         <v>74.453514</v>
       </c>
       <c r="U68" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V68">
         <v>5127</v>
@@ -5519,7 +5528,7 @@
         <v>25</v>
       </c>
       <c r="Q69" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R69" t="s">
         <v>31</v>
@@ -5531,7 +5540,7 @@
         <v>74.453514</v>
       </c>
       <c r="U69" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V69">
         <v>294680</v>
@@ -5590,7 +5599,7 @@
         <v>25</v>
       </c>
       <c r="Q70" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R70" t="s">
         <v>31</v>
@@ -5602,7 +5611,7 @@
         <v>74.453514</v>
       </c>
       <c r="U70" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V70">
         <v>16680</v>
@@ -5661,7 +5670,7 @@
         <v>25</v>
       </c>
       <c r="Q71" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R71" t="s">
         <v>31</v>
@@ -5673,7 +5682,7 @@
         <v>74.453514</v>
       </c>
       <c r="U71" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V71">
         <v>10000</v>
@@ -5732,7 +5741,7 @@
         <v>25</v>
       </c>
       <c r="Q72" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R72" t="s">
         <v>31</v>
@@ -5744,7 +5753,7 @@
         <v>74.453514</v>
       </c>
       <c r="U72" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V72">
         <v>10000</v>
@@ -5803,7 +5812,7 @@
         <v>25</v>
       </c>
       <c r="Q73" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R73" t="s">
         <v>31</v>
@@ -5815,7 +5824,7 @@
         <v>74.453514</v>
       </c>
       <c r="U73" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V73">
         <v>10000</v>
@@ -5874,7 +5883,7 @@
         <v>25</v>
       </c>
       <c r="Q74" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R74" t="s">
         <v>31</v>
@@ -5886,7 +5895,7 @@
         <v>74.453514</v>
       </c>
       <c r="U74" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V74">
         <v>30720</v>
@@ -5945,7 +5954,7 @@
         <v>25</v>
       </c>
       <c r="Q75" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R75" t="s">
         <v>31</v>
@@ -5957,7 +5966,7 @@
         <v>74.453514</v>
       </c>
       <c r="U75" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V75">
         <v>29640</v>
@@ -6016,7 +6025,7 @@
         <v>25</v>
       </c>
       <c r="Q76" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R76" t="s">
         <v>31</v>
@@ -6028,7 +6037,7 @@
         <v>74.453514</v>
       </c>
       <c r="U76" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V76">
         <v>28460</v>
@@ -6087,7 +6096,7 @@
         <v>25</v>
       </c>
       <c r="Q77" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R77" t="s">
         <v>31</v>
@@ -6099,7 +6108,7 @@
         <v>74.453514</v>
       </c>
       <c r="U77" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V77">
         <v>15353</v>
@@ -6158,7 +6167,7 @@
         <v>25</v>
       </c>
       <c r="Q78" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R78" t="s">
         <v>31</v>
@@ -6170,7 +6179,7 @@
         <v>74.453514</v>
       </c>
       <c r="U78" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V78">
         <v>20480</v>
@@ -6229,7 +6238,7 @@
         <v>25</v>
       </c>
       <c r="Q79" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R79" t="s">
         <v>31</v>
@@ -6241,7 +6250,7 @@
         <v>74.453514</v>
       </c>
       <c r="U79" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V79">
         <v>20480</v>
@@ -6300,7 +6309,7 @@
         <v>25</v>
       </c>
       <c r="Q80" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="R80" t="s">
         <v>31</v>
@@ -6312,7 +6321,7 @@
         <v>74.453514</v>
       </c>
       <c r="U80" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V80">
         <v>15360</v>
@@ -6371,7 +6380,7 @@
         <v>25</v>
       </c>
       <c r="Q81" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R81" t="s">
         <v>31</v>
@@ -6383,7 +6392,7 @@
         <v>74.18179719</v>
       </c>
       <c r="U81" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V81">
         <v>1314.5</v>
@@ -6442,7 +6451,7 @@
         <v>25</v>
       </c>
       <c r="Q82" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="R82" t="s">
         <v>31</v>
@@ -6454,7 +6463,7 @@
         <v>74.18230296</v>
       </c>
       <c r="U82" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V82">
         <v>52394.5</v>
@@ -6513,7 +6522,7 @@
         <v>25</v>
       </c>
       <c r="Q83" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="R83" t="s">
         <v>31</v>
@@ -6525,7 +6534,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="U83" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V83">
         <v>150000</v>
@@ -6584,7 +6593,7 @@
         <v>25</v>
       </c>
       <c r="Q84" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="R84" t="s">
         <v>31</v>
@@ -6596,7 +6605,7 @@
         <v>74.46541999999999</v>
       </c>
       <c r="U84" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="V84">
         <v>150000</v>

--- a/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Result_Sheet_leg1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1079" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="84">
   <si>
     <t>Scenario</t>
   </si>
@@ -100,205 +100,172 @@
     <t>JALANDHAR</t>
   </si>
   <si>
+    <t>SRI MUKTSAR SAHIB</t>
+  </si>
+  <si>
+    <t>Stor</t>
+  </si>
+  <si>
+    <t>ABOHAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHADUR KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BAHAAW WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BUKENWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BALLUANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAAGU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHANNAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DEEWAN KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHABA KOKARIYA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHARANGWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DHINGANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DODHEWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>DUTARANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GHALLU GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>GOBINDGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHUMIYANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>JHURAD KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHUPAYA SARWAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KULAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUNDAL GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MALOOKPURA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAUJGARH GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>NIHAL KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PANJKOSI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>PATRE WALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>SAIDANWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>WAREYAM KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>Bhadoo Waxing Plant</t>
+  </si>
+  <si>
+    <t>P.S. Waxing Plant</t>
+  </si>
+  <si>
+    <t>Sandhu waxing plant</t>
+  </si>
+  <si>
+    <t>Sri Ram cotton &amp; oil mill</t>
+  </si>
+  <si>
+    <t>Near Mandir</t>
+  </si>
+  <si>
+    <t>Near Gurdwara Sahib</t>
+  </si>
+  <si>
+    <t>Dera Jhangi wala</t>
+  </si>
+  <si>
+    <t>Near Jandwala Meera Sangla purchase center</t>
+  </si>
+  <si>
+    <t>GHARHIANA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAMMU KHERA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MURADWALA GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KUHADIANWALI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KHIUWALA DHAB GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>RAMKOT GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>KANDHWALA HAZARKHAN GRAIN MARKET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAMPUR  </t>
+  </si>
+  <si>
+    <t>KARAM PATTI GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>BHAGSAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>MAHABADAR GRAIN MARKET</t>
+  </si>
+  <si>
+    <t>sri muktsar sahib grain market</t>
+  </si>
+  <si>
+    <t>Depot</t>
+  </si>
+  <si>
+    <t>agah</t>
+  </si>
+  <si>
     <t>MALERKOTLA</t>
   </si>
   <si>
-    <t>SRI MUKTSAR SAHIB</t>
-  </si>
-  <si>
-    <t>Abohar</t>
-  </si>
-  <si>
-    <t>ADAMPUR</t>
-  </si>
-  <si>
-    <t>AHMEDGARH</t>
-  </si>
-  <si>
-    <t>Malout</t>
-  </si>
-  <si>
-    <t>ABOHAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHADUR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BAHAAW WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BUKENWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BALLUANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>BHAAGU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHANNAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>CHURHI WALA DHANNA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DEEWAN KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHABA KOKARIYA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHARANGWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DHINGANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DODHEWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>DUTARANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GADA DOB GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GHALLU GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>GOBINDGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JANDWALA MEERA SANGLA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHUMIYANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>JHURAD KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KALAR KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUMBAN GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KHUPAYA SARWAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KULAR GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUNDAL GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MALOOKPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAUJGARH GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NARAINPURA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>NIHAL KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PANJKOSI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>PATRE WALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>RUKANPURA KHUI KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SAIDANWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>SITO GUNO GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>VAJIDPUR BHOMA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>WAREYAM KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Bhadoo Waxing Plant</t>
-  </si>
-  <si>
-    <t>P.S. Waxing Plant</t>
-  </si>
-  <si>
-    <t>Sandhu waxing plant</t>
-  </si>
-  <si>
-    <t>Sri Ram cotton &amp; oil mill</t>
-  </si>
-  <si>
-    <t>Near Mandir</t>
-  </si>
-  <si>
-    <t>Near Gurdwara Sahib</t>
-  </si>
-  <si>
-    <t>Dera Jhangi wala</t>
-  </si>
-  <si>
-    <t>Near Jandwala Meera Sangla purchase center</t>
-  </si>
-  <si>
-    <t>GHARHIANA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MAMMU KHERA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>MURADWALA GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>KUHADIANWALI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADAMPUR  </t>
-  </si>
-  <si>
-    <t>BHIKHAMPUR BEGOWAL</t>
-  </si>
-  <si>
-    <t>DHALER KHURD</t>
-  </si>
-  <si>
-    <t>KANGANWAL</t>
-  </si>
-  <si>
-    <t>KUP</t>
-  </si>
-  <si>
-    <t>MAHOLI KALAN</t>
-  </si>
-  <si>
-    <t>MANAK HERI</t>
-  </si>
-  <si>
-    <t>MOMNA BAD</t>
-  </si>
-  <si>
-    <t>UMARPURA (NATHUMAJRA)</t>
-  </si>
-  <si>
-    <t>KARAM PATTI GRAIN MARKET</t>
-  </si>
-  <si>
-    <t>Depot</t>
-  </si>
-  <si>
-    <t>agah</t>
-  </si>
-  <si>
-    <t>Paddy</t>
+    <t>Wheat</t>
   </si>
 </sst>
 </file>
@@ -656,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -744,13 +711,13 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>501</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H2">
         <v>30.156605</v>
@@ -768,13 +735,13 @@
         <v>74.193507</v>
       </c>
       <c r="M2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N2">
         <v>396</v>
       </c>
       <c r="O2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P2" t="s">
         <v>25</v>
@@ -783,7 +750,7 @@
         <v>26</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S2">
         <v>30.15881226</v>
@@ -792,13 +759,13 @@
         <v>74.18214294000001</v>
       </c>
       <c r="U2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V2">
         <v>90000</v>
       </c>
       <c r="W2">
-        <v>229.452</v>
+        <v>390.7864</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -815,13 +782,13 @@
         <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F3">
         <v>501</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>30.156605</v>
@@ -839,13 +806,13 @@
         <v>74.18094151</v>
       </c>
       <c r="M3" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N3">
         <v>398</v>
       </c>
       <c r="O3" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P3" t="s">
         <v>25</v>
@@ -854,7 +821,7 @@
         <v>26</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S3">
         <v>30.15894356</v>
@@ -863,13 +830,13 @@
         <v>74.18094151</v>
       </c>
       <c r="U3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V3">
         <v>60000</v>
       </c>
       <c r="W3">
-        <v>223.6778</v>
+        <v>433.9496</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -886,13 +853,13 @@
         <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>501</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4">
         <v>30.156605</v>
@@ -910,13 +877,13 @@
         <v>74.18094151</v>
       </c>
       <c r="M4" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N4">
         <v>399</v>
       </c>
       <c r="O4" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P4" t="s">
         <v>25</v>
@@ -925,7 +892,7 @@
         <v>26</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S4">
         <v>30.15848535</v>
@@ -934,13 +901,13 @@
         <v>74.18085842000001</v>
       </c>
       <c r="U4" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V4">
         <v>120000</v>
       </c>
       <c r="W4">
-        <v>223.9893</v>
+        <v>410.0393</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -957,13 +924,13 @@
         <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>501</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5">
         <v>30.156605</v>
@@ -981,13 +948,13 @@
         <v>74.18094151</v>
       </c>
       <c r="M5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N5">
         <v>400</v>
       </c>
       <c r="O5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -996,7 +963,7 @@
         <v>26</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S5">
         <v>30.15809938</v>
@@ -1005,13 +972,13 @@
         <v>74.16401603</v>
       </c>
       <c r="U5" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V5">
-        <v>145397</v>
+        <v>33610</v>
       </c>
       <c r="W5">
-        <v>225.7026</v>
+        <v>397.1882</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -1028,13 +995,13 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>501</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6">
         <v>30.156605</v>
@@ -1043,22 +1010,22 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J6">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="K6">
-        <v>30.163017</v>
+        <v>30.154922</v>
       </c>
       <c r="L6">
-        <v>74.186234</v>
+        <v>74.193507</v>
       </c>
       <c r="M6" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N6">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O6" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -1067,22 +1034,22 @@
         <v>26</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S6">
-        <v>30.1689126</v>
+        <v>30.15857797</v>
       </c>
       <c r="T6">
-        <v>74.183232</v>
+        <v>74.18315728</v>
       </c>
       <c r="U6" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V6">
-        <v>31477</v>
+        <v>150000</v>
       </c>
       <c r="W6">
-        <v>221.9372</v>
+        <v>416.9045</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -1099,13 +1066,13 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7">
         <v>501</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7">
         <v>30.156605</v>
@@ -1114,22 +1081,22 @@
         <v>74.19572100000001</v>
       </c>
       <c r="J7">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K7">
-        <v>30.154922</v>
+        <v>30.126927</v>
       </c>
       <c r="L7">
-        <v>74.193507</v>
+        <v>74.161942</v>
       </c>
       <c r="M7" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O7" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -1138,22 +1105,22 @@
         <v>26</v>
       </c>
       <c r="R7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S7">
-        <v>30.15857797</v>
+        <v>30.126927</v>
       </c>
       <c r="T7">
-        <v>74.18315728</v>
+        <v>74.161942</v>
       </c>
       <c r="U7" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V7">
-        <v>150000</v>
+        <v>143264</v>
       </c>
       <c r="W7">
-        <v>229.2816</v>
+        <v>386.1116</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -1170,13 +1137,13 @@
         <v>26</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8">
         <v>502</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>30.099748</v>
@@ -1185,22 +1152,22 @@
         <v>74.34759699999999</v>
       </c>
       <c r="J8">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K8">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L8">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M8" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N8">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O8" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -1209,22 +1176,22 @@
         <v>26</v>
       </c>
       <c r="R8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S8">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="T8">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="U8" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V8">
-        <v>71835.5</v>
+        <v>48247.5</v>
       </c>
       <c r="W8">
-        <v>184.3114</v>
+        <v>321.9467</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -1241,37 +1208,37 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F9">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="H9">
-        <v>30.028699</v>
+        <v>30.099748</v>
       </c>
       <c r="I9">
-        <v>74.197309</v>
+        <v>74.34759699999999</v>
       </c>
       <c r="J9">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K9">
-        <v>30.105887</v>
+        <v>30.100105</v>
       </c>
       <c r="L9">
-        <v>74.18092900000001</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N9">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="O9" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -1280,22 +1247,22 @@
         <v>26</v>
       </c>
       <c r="R9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S9">
-        <v>30.10552983</v>
+        <v>30.0974593</v>
       </c>
       <c r="T9">
-        <v>74.18014506</v>
+        <v>74.206666</v>
       </c>
       <c r="U9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V9">
-        <v>73538.5</v>
+        <v>23588</v>
       </c>
       <c r="W9">
-        <v>193.705</v>
+        <v>359.5513</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -1312,13 +1279,13 @@
         <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F10">
         <v>503</v>
       </c>
       <c r="G10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H10">
         <v>30.028699</v>
@@ -1327,22 +1294,22 @@
         <v>74.197309</v>
       </c>
       <c r="J10">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K10">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L10">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M10" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N10">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O10" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -1351,22 +1318,22 @@
         <v>26</v>
       </c>
       <c r="R10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S10">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T10">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U10" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V10">
-        <v>322</v>
+        <v>73860.5</v>
       </c>
       <c r="W10">
-        <v>188.5026</v>
+        <v>401.6672</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -1383,13 +1350,13 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F11">
         <v>505</v>
       </c>
       <c r="G11" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H11">
         <v>30.162859</v>
@@ -1407,13 +1374,13 @@
         <v>74.161942</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N11">
         <v>407</v>
       </c>
       <c r="O11" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -1422,7 +1389,7 @@
         <v>26</v>
       </c>
       <c r="R11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S11">
         <v>30.126927</v>
@@ -1431,13 +1398,13 @@
         <v>74.161942</v>
       </c>
       <c r="U11" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V11">
         <v>37309</v>
       </c>
       <c r="W11">
-        <v>201.6013</v>
+        <v>373.1781</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -1454,13 +1421,13 @@
         <v>26</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12">
         <v>506</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H12">
         <v>30.16948</v>
@@ -1469,22 +1436,22 @@
         <v>74.28432100000001</v>
       </c>
       <c r="J12">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K12">
-        <v>30.163017</v>
+        <v>30.126927</v>
       </c>
       <c r="L12">
-        <v>74.186234</v>
+        <v>74.161942</v>
       </c>
       <c r="M12" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N12">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="O12" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -1493,22 +1460,22 @@
         <v>26</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S12">
-        <v>30.1689126</v>
+        <v>30.126927</v>
       </c>
       <c r="T12">
-        <v>74.183232</v>
+        <v>74.161942</v>
       </c>
       <c r="U12" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V12">
-        <v>2823</v>
+        <v>18025.5</v>
       </c>
       <c r="W12">
-        <v>225.0091</v>
+        <v>389.1835</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -1525,37 +1492,37 @@
         <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F13">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H13">
-        <v>30.16948</v>
+        <v>30.034436</v>
       </c>
       <c r="I13">
-        <v>74.28432100000001</v>
+        <v>74.233859</v>
       </c>
       <c r="J13">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="K13">
-        <v>30.163017</v>
+        <v>30.090357</v>
       </c>
       <c r="L13">
-        <v>74.186234</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N13">
-        <v>406</v>
+        <v>394</v>
       </c>
       <c r="O13" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -1564,22 +1531,22 @@
         <v>26</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S13">
-        <v>30.16991135</v>
+        <v>30.08793156</v>
       </c>
       <c r="T13">
-        <v>74.18230296</v>
+        <v>74.20908439</v>
       </c>
       <c r="U13" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V13">
-        <v>15202.5</v>
+        <v>16177.5</v>
       </c>
       <c r="W13">
-        <v>224.8565</v>
+        <v>336.5715</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -1596,13 +1563,13 @@
         <v>26</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F14">
         <v>507</v>
       </c>
       <c r="G14" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="H14">
         <v>30.034436</v>
@@ -1620,13 +1587,13 @@
         <v>74.20853700000001</v>
       </c>
       <c r="M14" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N14">
         <v>395</v>
       </c>
       <c r="O14" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -1635,7 +1602,7 @@
         <v>26</v>
       </c>
       <c r="R14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S14">
         <v>30.08675444</v>
@@ -1644,13 +1611,13 @@
         <v>74.20888524</v>
       </c>
       <c r="U14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V14">
-        <v>49766</v>
+        <v>33588.5</v>
       </c>
       <c r="W14">
-        <v>208.071</v>
+        <v>373.1206</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -1667,13 +1634,13 @@
         <v>26</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15">
         <v>508</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="H15">
         <v>30.182524</v>
@@ -1691,13 +1658,13 @@
         <v>74.186234</v>
       </c>
       <c r="M15" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N15">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O15" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -1706,22 +1673,22 @@
         <v>26</v>
       </c>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S15">
-        <v>30.16991135</v>
+        <v>30.1689126</v>
       </c>
       <c r="T15">
-        <v>74.18230296</v>
+        <v>74.183232</v>
       </c>
       <c r="U15" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V15">
-        <v>41707.5</v>
+        <v>13129</v>
       </c>
       <c r="W15">
-        <v>207.7269</v>
+        <v>375.923</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -1738,37 +1705,37 @@
         <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H16">
-        <v>30.199756</v>
+        <v>30.182524</v>
       </c>
       <c r="I16">
-        <v>74.108656</v>
+        <v>74.326095</v>
       </c>
       <c r="J16">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K16">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L16">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M16" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N16">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O16" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -1777,22 +1744,22 @@
         <v>26</v>
       </c>
       <c r="R16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S16">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T16">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U16" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V16">
-        <v>18038</v>
+        <v>28578.5</v>
       </c>
       <c r="W16">
-        <v>215.5494</v>
+        <v>372.0537</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -1809,37 +1776,37 @@
         <v>26</v>
       </c>
       <c r="E17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F17">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G17" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="H17">
-        <v>30.113508</v>
+        <v>30.199756</v>
       </c>
       <c r="I17">
-        <v>73.989543</v>
+        <v>74.108656</v>
       </c>
       <c r="J17">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K17">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L17">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M17" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N17">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O17" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -1848,22 +1815,22 @@
         <v>26</v>
       </c>
       <c r="R17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S17">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T17">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V17">
-        <v>44568.5</v>
+        <v>18038</v>
       </c>
       <c r="W17">
-        <v>216.9319</v>
+        <v>380.5587</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -1880,19 +1847,19 @@
         <v>26</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H18">
-        <v>30.122605</v>
+        <v>30.113508</v>
       </c>
       <c r="I18">
-        <v>74.328892</v>
+        <v>73.989543</v>
       </c>
       <c r="J18">
         <v>287</v>
@@ -1904,13 +1871,13 @@
         <v>74.161942</v>
       </c>
       <c r="M18" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N18">
         <v>407</v>
       </c>
       <c r="O18" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -1919,7 +1886,7 @@
         <v>26</v>
       </c>
       <c r="R18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S18">
         <v>30.126927</v>
@@ -1928,13 +1895,13 @@
         <v>74.161942</v>
       </c>
       <c r="U18" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V18">
-        <v>25216</v>
+        <v>44568.5</v>
       </c>
       <c r="W18">
-        <v>219.1982</v>
+        <v>388.5087</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -1951,37 +1918,37 @@
         <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F19">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H19">
-        <v>30.237206</v>
+        <v>30.122605</v>
       </c>
       <c r="I19">
-        <v>74.23982700000001</v>
+        <v>74.328892</v>
       </c>
       <c r="J19">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K19">
-        <v>30.175344</v>
+        <v>30.100105</v>
       </c>
       <c r="L19">
-        <v>74.178363</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M19" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N19">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="O19" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -1990,22 +1957,22 @@
         <v>26</v>
       </c>
       <c r="R19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S19">
-        <v>30.17081207</v>
+        <v>30.0974593</v>
       </c>
       <c r="T19">
-        <v>74.18179719</v>
+        <v>74.206666</v>
       </c>
       <c r="U19" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V19">
-        <v>44802</v>
+        <v>25216</v>
       </c>
       <c r="W19">
-        <v>193.4012</v>
+        <v>394.4381</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2022,37 +1989,37 @@
         <v>26</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F20">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G20" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H20">
-        <v>30.023582</v>
+        <v>30.237206</v>
       </c>
       <c r="I20">
-        <v>74.04262799999999</v>
+        <v>74.23982700000001</v>
       </c>
       <c r="J20">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K20">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L20">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N20">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O20" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -2061,22 +2028,22 @@
         <v>26</v>
       </c>
       <c r="R20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S20">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T20">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V20">
-        <v>30276.5</v>
+        <v>44802</v>
       </c>
       <c r="W20">
-        <v>189.8613</v>
+        <v>364.7468</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2093,37 +2060,37 @@
         <v>26</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="G21" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H21">
-        <v>29.960526</v>
+        <v>30.023582</v>
       </c>
       <c r="I21">
-        <v>74.219824</v>
+        <v>74.04262799999999</v>
       </c>
       <c r="J21">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="K21">
-        <v>30.105887</v>
+        <v>30.126927</v>
       </c>
       <c r="L21">
-        <v>74.18092900000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M21" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N21">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="O21" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -2132,22 +2099,22 @@
         <v>26</v>
       </c>
       <c r="R21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S21">
-        <v>30.10552983</v>
+        <v>30.126927</v>
       </c>
       <c r="T21">
-        <v>74.18014506</v>
+        <v>74.161942</v>
       </c>
       <c r="U21" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V21">
-        <v>19961.5</v>
+        <v>30276.5</v>
       </c>
       <c r="W21">
-        <v>200.8196</v>
+        <v>361.4381</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2164,37 +2131,37 @@
         <v>26</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H22">
-        <v>30.082625</v>
+        <v>29.960526</v>
       </c>
       <c r="I22">
-        <v>74.288794</v>
+        <v>74.219824</v>
       </c>
       <c r="J22">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K22">
-        <v>30.100105</v>
+        <v>30.090357</v>
       </c>
       <c r="L22">
-        <v>74.20670699999999</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M22" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N22">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="O22" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -2203,22 +2170,22 @@
         <v>26</v>
       </c>
       <c r="R22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S22">
-        <v>30.0974593</v>
+        <v>30.08675444</v>
       </c>
       <c r="T22">
-        <v>74.206666</v>
+        <v>74.20888524</v>
       </c>
       <c r="U22" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V22">
-        <v>9709</v>
+        <v>19961.5</v>
       </c>
       <c r="W22">
-        <v>226.4439</v>
+        <v>369.8016</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -2235,13 +2202,13 @@
         <v>26</v>
       </c>
       <c r="E23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F23">
         <v>515</v>
       </c>
       <c r="G23" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H23">
         <v>30.082625</v>
@@ -2250,22 +2217,22 @@
         <v>74.288794</v>
       </c>
       <c r="J23">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K23">
-        <v>30.126927</v>
+        <v>30.090357</v>
       </c>
       <c r="L23">
-        <v>74.161942</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M23" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N23">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="O23" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -2274,22 +2241,22 @@
         <v>26</v>
       </c>
       <c r="R23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S23">
-        <v>30.126927</v>
+        <v>30.08793156</v>
       </c>
       <c r="T23">
-        <v>74.161942</v>
+        <v>74.20908439</v>
       </c>
       <c r="U23" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V23">
-        <v>54672</v>
+        <v>64381</v>
       </c>
       <c r="W23">
-        <v>217.0863</v>
+        <v>354.7215</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -2306,37 +2273,37 @@
         <v>26</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G24" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H24">
-        <v>30.221432</v>
+        <v>30.254598</v>
       </c>
       <c r="I24">
-        <v>74.35153099999999</v>
+        <v>74.124285</v>
       </c>
       <c r="J24">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K24">
-        <v>30.175344</v>
+        <v>30.180346</v>
       </c>
       <c r="L24">
-        <v>74.178363</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M24" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N24">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O24" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -2345,22 +2312,22 @@
         <v>26</v>
       </c>
       <c r="R24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S24">
-        <v>30.17081207</v>
+        <v>30.15809938</v>
       </c>
       <c r="T24">
-        <v>74.18179719</v>
+        <v>74.16401603</v>
       </c>
       <c r="U24" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V24">
-        <v>13755.5</v>
+        <v>39817.5</v>
       </c>
       <c r="W24">
-        <v>218.3188</v>
+        <v>396.1463</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -2377,19 +2344,19 @@
         <v>26</v>
       </c>
       <c r="E25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F25">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="G25" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H25">
-        <v>30.221432</v>
+        <v>30.173582</v>
       </c>
       <c r="I25">
-        <v>74.35153099999999</v>
+        <v>74.250483</v>
       </c>
       <c r="J25">
         <v>284</v>
@@ -2401,13 +2368,13 @@
         <v>74.186234</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N25">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="O25" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -2416,22 +2383,22 @@
         <v>26</v>
       </c>
       <c r="R25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S25">
-        <v>30.16991135</v>
+        <v>30.1689126</v>
       </c>
       <c r="T25">
-        <v>74.18230296</v>
+        <v>74.183232</v>
       </c>
       <c r="U25" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V25">
-        <v>6714.5</v>
+        <v>10375.5</v>
       </c>
       <c r="W25">
-        <v>212.1802</v>
+        <v>388.2912</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -2448,37 +2415,37 @@
         <v>26</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="G26" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H26">
-        <v>30.254598</v>
+        <v>30.21019</v>
       </c>
       <c r="I26">
-        <v>74.124285</v>
+        <v>74.024728</v>
       </c>
       <c r="J26">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K26">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L26">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M26" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N26">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -2487,22 +2454,22 @@
         <v>26</v>
       </c>
       <c r="R26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S26">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T26">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U26" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V26">
-        <v>39817.5</v>
+        <v>100949.5</v>
       </c>
       <c r="W26">
-        <v>231.137</v>
+        <v>353.0248</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -2519,37 +2486,37 @@
         <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="G27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H27">
-        <v>30.173582</v>
+        <v>30.257887</v>
       </c>
       <c r="I27">
-        <v>74.250483</v>
+        <v>74.185624</v>
       </c>
       <c r="J27">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K27">
-        <v>30.163017</v>
+        <v>30.180346</v>
       </c>
       <c r="L27">
-        <v>74.186234</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M27" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N27">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="O27" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -2558,22 +2525,22 @@
         <v>26</v>
       </c>
       <c r="R27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S27">
-        <v>30.16991135</v>
+        <v>30.17767461</v>
       </c>
       <c r="T27">
-        <v>74.18230296</v>
+        <v>74.17723581</v>
       </c>
       <c r="U27" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V27">
-        <v>10375.5</v>
+        <v>36622.5</v>
       </c>
       <c r="W27">
-        <v>220.0951</v>
+        <v>360.298</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -2590,37 +2557,37 @@
         <v>26</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H28">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I28">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J28">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K28">
-        <v>30.180346</v>
+        <v>30.105887</v>
       </c>
       <c r="L28">
-        <v>74.17439299999999</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N28">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="O28" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P28" t="s">
         <v>25</v>
@@ -2629,22 +2596,22 @@
         <v>26</v>
       </c>
       <c r="R28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S28">
-        <v>30.15809938</v>
+        <v>30.10552983</v>
       </c>
       <c r="T28">
-        <v>74.16401603</v>
+        <v>74.18014506</v>
       </c>
       <c r="U28" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V28">
-        <v>72343</v>
+        <v>11652.5</v>
       </c>
       <c r="W28">
-        <v>192.1077</v>
+        <v>375.054</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -2661,19 +2628,19 @@
         <v>26</v>
       </c>
       <c r="E29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F29">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G29" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H29">
-        <v>30.21019</v>
+        <v>30.007285</v>
       </c>
       <c r="I29">
-        <v>74.024728</v>
+        <v>74.126166</v>
       </c>
       <c r="J29">
         <v>287</v>
@@ -2685,13 +2652,13 @@
         <v>74.161942</v>
       </c>
       <c r="M29" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N29">
         <v>407</v>
       </c>
       <c r="O29" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P29" t="s">
         <v>25</v>
@@ -2700,7 +2667,7 @@
         <v>26</v>
       </c>
       <c r="R29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S29">
         <v>30.126927</v>
@@ -2709,13 +2676,13 @@
         <v>74.161942</v>
       </c>
       <c r="U29" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V29">
-        <v>28606.5</v>
+        <v>16592.5</v>
       </c>
       <c r="W29">
-        <v>181.448</v>
+        <v>333.4662</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -2732,37 +2699,37 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F30">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="G30" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H30">
-        <v>30.257887</v>
+        <v>30.127701</v>
       </c>
       <c r="I30">
-        <v>74.185624</v>
+        <v>74.06368999999999</v>
       </c>
       <c r="J30">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K30">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L30">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M30" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N30">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O30" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -2771,22 +2738,22 @@
         <v>26</v>
       </c>
       <c r="R30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S30">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T30">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U30" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V30">
-        <v>2347.5</v>
+        <v>21311</v>
       </c>
       <c r="W30">
-        <v>193.9918</v>
+        <v>327.6523</v>
       </c>
     </row>
     <row r="31" spans="1:23">
@@ -2803,37 +2770,37 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F31">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="G31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H31">
-        <v>30.257887</v>
+        <v>29.98347</v>
       </c>
       <c r="I31">
-        <v>74.185624</v>
+        <v>74.283652</v>
       </c>
       <c r="J31">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K31">
-        <v>30.180346</v>
+        <v>30.090357</v>
       </c>
       <c r="L31">
-        <v>74.17439299999999</v>
+        <v>74.20853700000001</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N31">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="O31" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -2842,22 +2809,22 @@
         <v>26</v>
       </c>
       <c r="R31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S31">
-        <v>30.17767461</v>
+        <v>30.08793156</v>
       </c>
       <c r="T31">
-        <v>74.17723581</v>
+        <v>74.20908439</v>
       </c>
       <c r="U31" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V31">
-        <v>34275</v>
+        <v>34094</v>
       </c>
       <c r="W31">
-        <v>188.9582</v>
+        <v>293.712</v>
       </c>
     </row>
     <row r="32" spans="1:23">
@@ -2874,37 +2841,37 @@
         <v>26</v>
       </c>
       <c r="E32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F32">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="G32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H32">
-        <v>30.007285</v>
+        <v>30.216512</v>
       </c>
       <c r="I32">
-        <v>74.126166</v>
+        <v>74.269492</v>
       </c>
       <c r="J32">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K32">
-        <v>30.126927</v>
+        <v>30.163017</v>
       </c>
       <c r="L32">
-        <v>74.161942</v>
+        <v>74.186234</v>
       </c>
       <c r="M32" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N32">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="O32" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -2913,22 +2880,22 @@
         <v>26</v>
       </c>
       <c r="R32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S32">
-        <v>30.126927</v>
+        <v>30.1689126</v>
       </c>
       <c r="T32">
-        <v>74.161942</v>
+        <v>74.183232</v>
       </c>
       <c r="U32" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V32">
-        <v>28245</v>
+        <v>10795.5</v>
       </c>
       <c r="W32">
-        <v>161.8894</v>
+        <v>296.1244</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -2945,37 +2912,37 @@
         <v>26</v>
       </c>
       <c r="E33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F33">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H33">
-        <v>30.039412</v>
+        <v>30.216512</v>
       </c>
       <c r="I33">
-        <v>73.954567</v>
+        <v>74.269492</v>
       </c>
       <c r="J33">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K33">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L33">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M33" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N33">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O33" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -2984,22 +2951,22 @@
         <v>26</v>
       </c>
       <c r="R33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S33">
-        <v>30.126927</v>
+        <v>30.16991135</v>
       </c>
       <c r="T33">
-        <v>74.161942</v>
+        <v>74.18230296</v>
       </c>
       <c r="U33" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V33">
-        <v>12854</v>
+        <v>21605.5</v>
       </c>
       <c r="W33">
-        <v>152.3635</v>
+        <v>328.1816</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3016,37 +2983,37 @@
         <v>26</v>
       </c>
       <c r="E34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F34">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="G34" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H34">
-        <v>30.012837</v>
+        <v>30.132598</v>
       </c>
       <c r="I34">
-        <v>74.432883</v>
+        <v>74.343463</v>
       </c>
       <c r="J34">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K34">
-        <v>30.090357</v>
+        <v>30.100105</v>
       </c>
       <c r="L34">
-        <v>74.20853700000001</v>
+        <v>74.20670699999999</v>
       </c>
       <c r="M34" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N34">
         <v>397</v>
       </c>
       <c r="O34" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -3055,7 +3022,7 @@
         <v>26</v>
       </c>
       <c r="R34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S34">
         <v>30.0974593</v>
@@ -3064,13 +3031,13 @@
         <v>74.206666</v>
       </c>
       <c r="U34" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V34">
-        <v>74081</v>
+        <v>71196</v>
       </c>
       <c r="W34">
-        <v>142.7227</v>
+        <v>288.9329</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -3087,19 +3054,19 @@
         <v>26</v>
       </c>
       <c r="E35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H35">
-        <v>30.127701</v>
+        <v>30.132598</v>
       </c>
       <c r="I35">
-        <v>74.06368999999999</v>
+        <v>74.343463</v>
       </c>
       <c r="J35">
         <v>287</v>
@@ -3111,13 +3078,13 @@
         <v>74.161942</v>
       </c>
       <c r="M35" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N35">
         <v>407</v>
       </c>
       <c r="O35" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -3126,7 +3093,7 @@
         <v>26</v>
       </c>
       <c r="R35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S35">
         <v>30.126927</v>
@@ -3135,13 +3102,13 @@
         <v>74.161942</v>
       </c>
       <c r="U35" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V35">
-        <v>21311</v>
+        <v>2489</v>
       </c>
       <c r="W35">
-        <v>156.0755</v>
+        <v>285.2698</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -3158,37 +3125,37 @@
         <v>26</v>
       </c>
       <c r="E36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F36">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H36">
-        <v>29.98347</v>
+        <v>30.065633</v>
       </c>
       <c r="I36">
-        <v>74.283652</v>
+        <v>73.98462499999999</v>
       </c>
       <c r="J36">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K36">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L36">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M36" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N36">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O36" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -3197,22 +3164,22 @@
         <v>26</v>
       </c>
       <c r="R36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S36">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T36">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U36" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V36">
-        <v>30310</v>
+        <v>34208</v>
       </c>
       <c r="W36">
-        <v>165.0819</v>
+        <v>344.2239</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -3229,37 +3196,37 @@
         <v>26</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F37">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="G37" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H37">
-        <v>29.98347</v>
+        <v>30.224829</v>
       </c>
       <c r="I37">
-        <v>74.283652</v>
+        <v>74.12361199999999</v>
       </c>
       <c r="J37">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K37">
-        <v>30.090357</v>
+        <v>30.180346</v>
       </c>
       <c r="L37">
-        <v>74.20853700000001</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M37" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N37">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="O37" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -3268,22 +3235,22 @@
         <v>26</v>
       </c>
       <c r="R37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S37">
-        <v>30.08675444</v>
+        <v>30.15809938</v>
       </c>
       <c r="T37">
-        <v>74.20888524</v>
+        <v>74.16401603</v>
       </c>
       <c r="U37" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V37">
-        <v>3784</v>
+        <v>54819.5</v>
       </c>
       <c r="W37">
-        <v>165.2115</v>
+        <v>349.1469</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -3300,37 +3267,37 @@
         <v>26</v>
       </c>
       <c r="E38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F38">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H38">
-        <v>30.216512</v>
+        <v>30.178444</v>
       </c>
       <c r="I38">
-        <v>74.269492</v>
+        <v>74.065141</v>
       </c>
       <c r="J38">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="K38">
-        <v>30.175344</v>
+        <v>30.126927</v>
       </c>
       <c r="L38">
-        <v>74.178363</v>
+        <v>74.161942</v>
       </c>
       <c r="M38" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N38">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O38" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -3339,22 +3306,22 @@
         <v>26</v>
       </c>
       <c r="R38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S38">
-        <v>30.17081207</v>
+        <v>30.126927</v>
       </c>
       <c r="T38">
-        <v>74.18179719</v>
+        <v>74.161942</v>
       </c>
       <c r="U38" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V38">
-        <v>32401</v>
+        <v>37768</v>
       </c>
       <c r="W38">
-        <v>134.0669</v>
+        <v>328.0969</v>
       </c>
     </row>
     <row r="39" spans="1:23">
@@ -3371,19 +3338,19 @@
         <v>26</v>
       </c>
       <c r="E39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F39">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H39">
-        <v>30.132598</v>
+        <v>30.196706</v>
       </c>
       <c r="I39">
-        <v>74.343463</v>
+        <v>74.04839699999999</v>
       </c>
       <c r="J39">
         <v>287</v>
@@ -3395,13 +3362,13 @@
         <v>74.161942</v>
       </c>
       <c r="M39" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N39">
         <v>407</v>
       </c>
       <c r="O39" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -3410,7 +3377,7 @@
         <v>26</v>
       </c>
       <c r="R39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S39">
         <v>30.126927</v>
@@ -3419,13 +3386,13 @@
         <v>74.161942</v>
       </c>
       <c r="U39" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V39">
-        <v>73685</v>
+        <v>29874.5</v>
       </c>
       <c r="W39">
-        <v>113.693</v>
+        <v>316.5226</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -3442,19 +3409,19 @@
         <v>26</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F40">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H40">
-        <v>30.065633</v>
+        <v>30.035803</v>
       </c>
       <c r="I40">
-        <v>73.98462499999999</v>
+        <v>74.111367</v>
       </c>
       <c r="J40">
         <v>287</v>
@@ -3466,13 +3433,13 @@
         <v>74.161942</v>
       </c>
       <c r="M40" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N40">
         <v>407</v>
       </c>
       <c r="O40" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -3481,7 +3448,7 @@
         <v>26</v>
       </c>
       <c r="R40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S40">
         <v>30.126927</v>
@@ -3490,13 +3457,13 @@
         <v>74.161942</v>
       </c>
       <c r="U40" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V40">
-        <v>34208</v>
+        <v>56983.5</v>
       </c>
       <c r="W40">
-        <v>172.6471</v>
+        <v>289.7921</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -3513,37 +3480,37 @@
         <v>26</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F41">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H41">
-        <v>29.956267</v>
+        <v>30.131281</v>
       </c>
       <c r="I41">
-        <v>74.332578</v>
+        <v>74.103374</v>
       </c>
       <c r="J41">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K41">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L41">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M41" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N41">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O41" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -3552,22 +3519,22 @@
         <v>26</v>
       </c>
       <c r="R41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S41">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T41">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U41" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V41">
-        <v>17701</v>
+        <v>23195.5</v>
       </c>
       <c r="W41">
-        <v>169.7707</v>
+        <v>289.7733</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -3584,37 +3551,37 @@
         <v>26</v>
       </c>
       <c r="E42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F42">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H42">
-        <v>30.224829</v>
+        <v>30.029455</v>
       </c>
       <c r="I42">
-        <v>74.12361199999999</v>
+        <v>74.077962</v>
       </c>
       <c r="J42">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K42">
-        <v>30.180346</v>
+        <v>30.126927</v>
       </c>
       <c r="L42">
-        <v>74.17439299999999</v>
+        <v>74.161942</v>
       </c>
       <c r="M42" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N42">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="O42" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -3623,22 +3590,22 @@
         <v>26</v>
       </c>
       <c r="R42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S42">
-        <v>30.15809938</v>
+        <v>30.126927</v>
       </c>
       <c r="T42">
-        <v>74.16401603</v>
+        <v>74.161942</v>
       </c>
       <c r="U42" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V42">
-        <v>54819.5</v>
+        <v>57368</v>
       </c>
       <c r="W42">
-        <v>184.1376</v>
+        <v>318.9856</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -3655,37 +3622,37 @@
         <v>26</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F43">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H43">
-        <v>30.178444</v>
+        <v>29.983545</v>
       </c>
       <c r="I43">
-        <v>74.065141</v>
+        <v>74.173574</v>
       </c>
       <c r="J43">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K43">
-        <v>30.126927</v>
+        <v>30.105887</v>
       </c>
       <c r="L43">
-        <v>74.161942</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M43" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N43">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="O43" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -3694,22 +3661,22 @@
         <v>26</v>
       </c>
       <c r="R43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S43">
-        <v>30.126927</v>
+        <v>30.10552983</v>
       </c>
       <c r="T43">
-        <v>74.161942</v>
+        <v>74.18014506</v>
       </c>
       <c r="U43" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V43">
-        <v>37768</v>
+        <v>2487</v>
       </c>
       <c r="W43">
-        <v>156.5201</v>
+        <v>364.5371</v>
       </c>
     </row>
     <row r="44" spans="1:23">
@@ -3726,37 +3693,37 @@
         <v>26</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F44">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="G44" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H44">
-        <v>30.196706</v>
+        <v>30.254422</v>
       </c>
       <c r="I44">
-        <v>74.04839699999999</v>
+        <v>74.126414</v>
       </c>
       <c r="J44">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K44">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L44">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M44" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N44">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O44" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -3765,22 +3732,22 @@
         <v>26</v>
       </c>
       <c r="R44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S44">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T44">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U44" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V44">
-        <v>29874.5</v>
+        <v>29195</v>
       </c>
       <c r="W44">
-        <v>144.9458</v>
+        <v>338.1554</v>
       </c>
     </row>
     <row r="45" spans="1:23">
@@ -3797,37 +3764,37 @@
         <v>26</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F45">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c r="G45" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H45">
-        <v>30.035803</v>
+        <v>30.247905</v>
       </c>
       <c r="I45">
-        <v>74.111367</v>
+        <v>74.129536</v>
       </c>
       <c r="J45">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K45">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L45">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M45" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N45">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O45" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -3836,22 +3803,22 @@
         <v>26</v>
       </c>
       <c r="R45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S45">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T45">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U45" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V45">
-        <v>56983.5</v>
+        <v>26795</v>
       </c>
       <c r="W45">
-        <v>118.2153</v>
+        <v>302.2476</v>
       </c>
     </row>
     <row r="46" spans="1:23">
@@ -3868,37 +3835,37 @@
         <v>26</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F46">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="G46" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H46">
-        <v>30.131281</v>
+        <v>30.25374</v>
       </c>
       <c r="I46">
-        <v>74.103374</v>
+        <v>74.122122</v>
       </c>
       <c r="J46">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K46">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L46">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M46" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N46">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O46" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -3907,22 +3874,22 @@
         <v>26</v>
       </c>
       <c r="R46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S46">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T46">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U46" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V46">
-        <v>23195.5</v>
+        <v>7950</v>
       </c>
       <c r="W46">
-        <v>118.1965</v>
+        <v>309.5632</v>
       </c>
     </row>
     <row r="47" spans="1:23">
@@ -3939,37 +3906,37 @@
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F47">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="G47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H47">
-        <v>30.027734</v>
+        <v>29.975306</v>
       </c>
       <c r="I47">
-        <v>74.36728100000001</v>
+        <v>74.164011</v>
       </c>
       <c r="J47">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K47">
-        <v>30.090357</v>
+        <v>30.105887</v>
       </c>
       <c r="L47">
-        <v>74.20853700000001</v>
+        <v>74.18092900000001</v>
       </c>
       <c r="M47" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N47">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="O47" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -3978,22 +3945,22 @@
         <v>26</v>
       </c>
       <c r="R47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S47">
-        <v>30.08793156</v>
+        <v>30.10552983</v>
       </c>
       <c r="T47">
-        <v>74.20908439</v>
+        <v>74.18014506</v>
       </c>
       <c r="U47" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V47">
-        <v>71340</v>
+        <v>5500</v>
       </c>
       <c r="W47">
-        <v>140.4517</v>
+        <v>357.189</v>
       </c>
     </row>
     <row r="48" spans="1:23">
@@ -4010,37 +3977,37 @@
         <v>26</v>
       </c>
       <c r="E48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F48">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="G48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H48">
-        <v>30.027734</v>
+        <v>30.144184</v>
       </c>
       <c r="I48">
-        <v>74.36728100000001</v>
+        <v>74.122771</v>
       </c>
       <c r="J48">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K48">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L48">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M48" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N48">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="O48" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -4049,22 +4016,22 @@
         <v>26</v>
       </c>
       <c r="R48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S48">
-        <v>30.0974593</v>
+        <v>30.126927</v>
       </c>
       <c r="T48">
-        <v>74.206666</v>
+        <v>74.161942</v>
       </c>
       <c r="U48" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V48">
-        <v>36210</v>
+        <v>12630.5</v>
       </c>
       <c r="W48">
-        <v>140.9992</v>
+        <v>296.7084</v>
       </c>
     </row>
     <row r="49" spans="1:23">
@@ -4081,37 +4048,37 @@
         <v>26</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F49">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="G49" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H49">
-        <v>29.951208</v>
+        <v>30.161715</v>
       </c>
       <c r="I49">
-        <v>74.380385</v>
+        <v>73.987483</v>
       </c>
       <c r="J49">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K49">
-        <v>30.090357</v>
+        <v>30.126927</v>
       </c>
       <c r="L49">
-        <v>74.20853700000001</v>
+        <v>74.161942</v>
       </c>
       <c r="M49" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N49">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="O49" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -4120,22 +4087,22 @@
         <v>26</v>
       </c>
       <c r="R49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S49">
-        <v>30.08793156</v>
+        <v>30.126927</v>
       </c>
       <c r="T49">
-        <v>74.20908439</v>
+        <v>74.161942</v>
       </c>
       <c r="U49" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V49">
-        <v>43549</v>
+        <v>13803</v>
       </c>
       <c r="W49">
-        <v>145.4061</v>
+        <v>283.3684</v>
       </c>
     </row>
     <row r="50" spans="1:23">
@@ -4152,19 +4119,19 @@
         <v>26</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F50">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="G50" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H50">
-        <v>30.029455</v>
+        <v>30.21135</v>
       </c>
       <c r="I50">
-        <v>74.077962</v>
+        <v>74.02397999999999</v>
       </c>
       <c r="J50">
         <v>287</v>
@@ -4176,13 +4143,13 @@
         <v>74.161942</v>
       </c>
       <c r="M50" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N50">
         <v>407</v>
       </c>
       <c r="O50" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -4191,7 +4158,7 @@
         <v>26</v>
       </c>
       <c r="R50" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S50">
         <v>30.126927</v>
@@ -4200,13 +4167,13 @@
         <v>74.161942</v>
       </c>
       <c r="U50" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V50">
-        <v>57368</v>
+        <v>9145</v>
       </c>
       <c r="W50">
-        <v>147.4088</v>
+        <v>337.8703</v>
       </c>
     </row>
     <row r="51" spans="1:23">
@@ -4223,37 +4190,37 @@
         <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F51">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="G51" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H51">
-        <v>29.983545</v>
+        <v>30.296726</v>
       </c>
       <c r="I51">
-        <v>74.173574</v>
+        <v>74.263169</v>
       </c>
       <c r="J51">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K51">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L51">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M51" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N51">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O51" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -4262,22 +4229,22 @@
         <v>26</v>
       </c>
       <c r="R51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S51">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T51">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U51" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V51">
-        <v>2487</v>
+        <v>17622.5</v>
       </c>
       <c r="W51">
-        <v>151.3725</v>
+        <v>365.3283</v>
       </c>
     </row>
     <row r="52" spans="1:23">
@@ -4294,19 +4261,19 @@
         <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F52">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H52">
-        <v>30.254422</v>
+        <v>30.285139</v>
       </c>
       <c r="I52">
-        <v>74.126414</v>
+        <v>74.172681</v>
       </c>
       <c r="J52">
         <v>285</v>
@@ -4318,13 +4285,13 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M52" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N52">
         <v>400</v>
       </c>
       <c r="O52" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -4333,7 +4300,7 @@
         <v>26</v>
       </c>
       <c r="R52" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S52">
         <v>30.15809938</v>
@@ -4342,13 +4309,13 @@
         <v>74.16401603</v>
       </c>
       <c r="U52" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V52">
-        <v>29195</v>
+        <v>2347.5</v>
       </c>
       <c r="W52">
-        <v>173.1461</v>
+        <v>356.2633</v>
       </c>
     </row>
     <row r="53" spans="1:23">
@@ -4365,19 +4332,19 @@
         <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F53">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G53" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H53">
-        <v>30.247905</v>
+        <v>30.285139</v>
       </c>
       <c r="I53">
-        <v>74.129536</v>
+        <v>74.172681</v>
       </c>
       <c r="J53">
         <v>285</v>
@@ -4389,13 +4356,13 @@
         <v>74.17439299999999</v>
       </c>
       <c r="M53" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N53">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="O53" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -4404,22 +4371,22 @@
         <v>26</v>
       </c>
       <c r="R53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S53">
-        <v>30.15809938</v>
+        <v>30.17767461</v>
       </c>
       <c r="T53">
-        <v>74.16401603</v>
+        <v>74.17723581</v>
       </c>
       <c r="U53" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V53">
-        <v>26795</v>
+        <v>40337.5</v>
       </c>
       <c r="W53">
-        <v>137.2383</v>
+        <v>360.289</v>
       </c>
     </row>
     <row r="54" spans="1:23">
@@ -4436,37 +4403,37 @@
         <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F54">
-        <v>543</v>
+        <v>551</v>
       </c>
       <c r="G54" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H54">
-        <v>30.25374</v>
+        <v>30.260814</v>
       </c>
       <c r="I54">
-        <v>74.122122</v>
+        <v>74.269329</v>
       </c>
       <c r="J54">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K54">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L54">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M54" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N54">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O54" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -4475,22 +4442,22 @@
         <v>26</v>
       </c>
       <c r="R54" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S54">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="T54">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="U54" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V54">
-        <v>7950</v>
+        <v>56502.5</v>
       </c>
       <c r="W54">
-        <v>144.5539</v>
+        <v>336.2379</v>
       </c>
     </row>
     <row r="55" spans="1:23">
@@ -4507,37 +4474,37 @@
         <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F55">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H55">
-        <v>29.975306</v>
+        <v>30.290503</v>
       </c>
       <c r="I55">
-        <v>74.164011</v>
+        <v>74.220803</v>
       </c>
       <c r="J55">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="K55">
-        <v>30.126927</v>
+        <v>30.175344</v>
       </c>
       <c r="L55">
-        <v>74.161942</v>
+        <v>74.178363</v>
       </c>
       <c r="M55" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N55">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="O55" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -4546,22 +4513,22 @@
         <v>26</v>
       </c>
       <c r="R55" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S55">
-        <v>30.126927</v>
+        <v>30.17081207</v>
       </c>
       <c r="T55">
-        <v>74.161942</v>
+        <v>74.18179719</v>
       </c>
       <c r="U55" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V55">
-        <v>5500</v>
+        <v>43110</v>
       </c>
       <c r="W55">
-        <v>144.0245</v>
+        <v>329.3488</v>
       </c>
     </row>
     <row r="56" spans="1:23">
@@ -4578,37 +4545,37 @@
         <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F56">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="G56" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H56">
-        <v>30.144184</v>
+        <v>30.251211</v>
       </c>
       <c r="I56">
-        <v>74.122771</v>
+        <v>74.011872</v>
       </c>
       <c r="J56">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K56">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L56">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M56" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N56">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O56" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -4617,22 +4584,22 @@
         <v>26</v>
       </c>
       <c r="R56" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S56">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T56">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U56" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V56">
-        <v>12630.5</v>
+        <v>128218</v>
       </c>
       <c r="W56">
-        <v>125.1316</v>
+        <v>350.5365</v>
       </c>
     </row>
     <row r="57" spans="1:23">
@@ -4649,37 +4616,37 @@
         <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F57">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="G57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H57">
-        <v>30.161715</v>
+        <v>30.280985</v>
       </c>
       <c r="I57">
-        <v>73.987483</v>
+        <v>74.057811</v>
       </c>
       <c r="J57">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="K57">
-        <v>30.126927</v>
+        <v>30.180346</v>
       </c>
       <c r="L57">
-        <v>74.161942</v>
+        <v>74.17439299999999</v>
       </c>
       <c r="M57" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N57">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="O57" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -4688,22 +4655,22 @@
         <v>26</v>
       </c>
       <c r="R57" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S57">
-        <v>30.126927</v>
+        <v>30.15809938</v>
       </c>
       <c r="T57">
-        <v>74.161942</v>
+        <v>74.16401603</v>
       </c>
       <c r="U57" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V57">
-        <v>13803</v>
+        <v>62709.5</v>
       </c>
       <c r="W57">
-        <v>111.7916</v>
+        <v>303.653</v>
       </c>
     </row>
     <row r="58" spans="1:23">
@@ -4720,37 +4687,37 @@
         <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F58">
-        <v>548</v>
+        <v>612</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H58">
-        <v>30.21135</v>
+        <v>30.3064</v>
       </c>
       <c r="I58">
-        <v>74.02397999999999</v>
+        <v>74.22073899999999</v>
       </c>
       <c r="J58">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K58">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L58">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M58" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N58">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O58" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -4759,22 +4726,22 @@
         <v>26</v>
       </c>
       <c r="R58" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S58">
-        <v>30.15809938</v>
+        <v>30.17081207</v>
       </c>
       <c r="T58">
-        <v>74.16401603</v>
+        <v>74.18179719</v>
       </c>
       <c r="U58" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V58">
-        <v>9145</v>
+        <v>47189.5</v>
       </c>
       <c r="W58">
-        <v>176.9532</v>
+        <v>353.1016</v>
       </c>
     </row>
     <row r="59" spans="1:23">
@@ -4788,64 +4755,64 @@
         <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F59">
-        <v>549</v>
+        <v>1046</v>
       </c>
       <c r="G59" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H59">
-        <v>30.296726</v>
+        <v>31.425406</v>
       </c>
       <c r="I59">
-        <v>74.263169</v>
+        <v>75.719528</v>
       </c>
       <c r="J59">
-        <v>279</v>
+        <v>522</v>
       </c>
       <c r="K59">
-        <v>30.175344</v>
+        <v>31.4204409</v>
       </c>
       <c r="L59">
-        <v>74.178363</v>
+        <v>75.69994199999999</v>
       </c>
       <c r="M59" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N59">
-        <v>401</v>
+        <v>625</v>
       </c>
       <c r="O59" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
       </c>
       <c r="Q59" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R59" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S59">
-        <v>30.17081207</v>
+        <v>31.408658</v>
       </c>
       <c r="T59">
-        <v>74.18179719</v>
+        <v>75.685958</v>
       </c>
       <c r="U59" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V59">
-        <v>17622.5</v>
+        <v>21500</v>
       </c>
       <c r="W59">
-        <v>193.9827</v>
+        <v>339.9454</v>
       </c>
     </row>
     <row r="60" spans="1:23">
@@ -4859,40 +4826,40 @@
         <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F60">
-        <v>550</v>
+        <v>1660</v>
       </c>
       <c r="G60" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H60">
-        <v>30.285139</v>
+        <v>30.2397029</v>
       </c>
       <c r="I60">
-        <v>74.172681</v>
+        <v>74.2953411</v>
       </c>
       <c r="J60">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="K60">
-        <v>30.180346</v>
+        <v>30.175344</v>
       </c>
       <c r="L60">
-        <v>74.17439299999999</v>
+        <v>74.178363</v>
       </c>
       <c r="M60" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N60">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O60" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -4901,22 +4868,22 @@
         <v>26</v>
       </c>
       <c r="R60" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S60">
-        <v>30.17767461</v>
+        <v>30.17081207</v>
       </c>
       <c r="T60">
-        <v>74.17723581</v>
+        <v>74.18179719</v>
       </c>
       <c r="U60" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V60">
-        <v>42685</v>
+        <v>1314.5</v>
       </c>
       <c r="W60">
-        <v>188.9492</v>
+        <v>390.4463</v>
       </c>
     </row>
     <row r="61" spans="1:23">
@@ -4930,22 +4897,22 @@
         <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F61">
-        <v>551</v>
+        <v>1660</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H61">
-        <v>30.260814</v>
+        <v>30.2397029</v>
       </c>
       <c r="I61">
-        <v>74.269329</v>
+        <v>74.2953411</v>
       </c>
       <c r="J61">
         <v>279</v>
@@ -4957,13 +4924,13 @@
         <v>74.178363</v>
       </c>
       <c r="M61" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N61">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="O61" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -4972,22 +4939,22 @@
         <v>26</v>
       </c>
       <c r="R61" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S61">
-        <v>30.17081207</v>
+        <v>30.16991135</v>
       </c>
       <c r="T61">
-        <v>74.18179719</v>
+        <v>74.18230296</v>
       </c>
       <c r="U61" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V61">
-        <v>56502.5</v>
+        <v>52394.5</v>
       </c>
       <c r="W61">
-        <v>164.8923</v>
+        <v>413.2154</v>
       </c>
     </row>
     <row r="62" spans="1:23">
@@ -5001,64 +4968,64 @@
         <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F62">
-        <v>552</v>
+        <v>1577</v>
       </c>
       <c r="G62" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H62">
-        <v>30.290503</v>
+        <v>30.4426709</v>
       </c>
       <c r="I62">
-        <v>74.220803</v>
+        <v>74.4101264</v>
       </c>
       <c r="J62">
-        <v>279</v>
+        <v>1455</v>
       </c>
       <c r="K62">
-        <v>30.175344</v>
+        <v>30.450458</v>
       </c>
       <c r="L62">
-        <v>74.178363</v>
+        <v>74.489422</v>
       </c>
       <c r="M62" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N62">
-        <v>401</v>
+        <v>866</v>
       </c>
       <c r="O62" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
       </c>
       <c r="Q62" t="s">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="R62" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S62">
-        <v>30.17081207</v>
+        <v>30.458388</v>
       </c>
       <c r="T62">
-        <v>74.18179719</v>
+        <v>74.453514</v>
       </c>
       <c r="U62" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V62">
-        <v>43110</v>
+        <v>88594</v>
       </c>
       <c r="W62">
-        <v>158.0032</v>
+        <v>124.0032</v>
       </c>
     </row>
     <row r="63" spans="1:23">
@@ -5072,64 +5039,64 @@
         <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F63">
-        <v>1046</v>
+        <v>1577</v>
       </c>
       <c r="G63" t="s">
+        <v>77</v>
+      </c>
+      <c r="H63">
+        <v>30.4426709</v>
+      </c>
+      <c r="I63">
+        <v>74.4101264</v>
+      </c>
+      <c r="J63">
+        <v>1455</v>
+      </c>
+      <c r="K63">
+        <v>30.450458</v>
+      </c>
+      <c r="L63">
+        <v>74.489422</v>
+      </c>
+      <c r="M63" t="s">
+        <v>80</v>
+      </c>
+      <c r="N63">
+        <v>870</v>
+      </c>
+      <c r="O63" t="s">
+        <v>81</v>
+      </c>
+      <c r="P63" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" t="s">
         <v>82</v>
       </c>
-      <c r="H63">
-        <v>31.425406</v>
-      </c>
-      <c r="I63">
-        <v>75.719528</v>
-      </c>
-      <c r="J63">
-        <v>522</v>
-      </c>
-      <c r="K63">
-        <v>31.4204409</v>
-      </c>
-      <c r="L63">
-        <v>75.69994199999999</v>
-      </c>
-      <c r="M63" t="s">
-        <v>92</v>
-      </c>
-      <c r="N63">
-        <v>625</v>
-      </c>
-      <c r="O63" t="s">
-        <v>93</v>
-      </c>
-      <c r="P63" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>27</v>
-      </c>
       <c r="R63" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="S63">
-        <v>31.408658</v>
+        <v>30.458388</v>
       </c>
       <c r="T63">
-        <v>75.685958</v>
+        <v>74.453514</v>
       </c>
       <c r="U63" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V63">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="W63">
-        <v>141.4683</v>
+        <v>124.0032</v>
       </c>
     </row>
     <row r="64" spans="1:23">
@@ -5146,46 +5113,46 @@
         <v>28</v>
       </c>
       <c r="E64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F64">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G64" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="H64">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I64">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J64">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K64">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L64">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M64" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N64">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="O64" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
       </c>
       <c r="Q64" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R64" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S64">
         <v>30.458388</v>
@@ -5194,13 +5161,13 @@
         <v>74.453514</v>
       </c>
       <c r="U64" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V64">
-        <v>197630</v>
+        <v>5000</v>
       </c>
       <c r="W64">
-        <v>184.1593</v>
+        <v>124.0032</v>
       </c>
     </row>
     <row r="65" spans="1:23">
@@ -5217,46 +5184,46 @@
         <v>28</v>
       </c>
       <c r="E65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F65">
-        <v>1322</v>
+        <v>1577</v>
       </c>
       <c r="G65" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="H65">
-        <v>30.67924</v>
+        <v>30.4426709</v>
       </c>
       <c r="I65">
-        <v>75.84139999999999</v>
+        <v>74.4101264</v>
       </c>
       <c r="J65">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K65">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L65">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M65" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N65">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="O65" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
       </c>
       <c r="Q65" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R65" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S65">
         <v>30.458388</v>
@@ -5265,13 +5232,13 @@
         <v>74.453514</v>
       </c>
       <c r="U65" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V65">
-        <v>16680</v>
+        <v>5000</v>
       </c>
       <c r="W65">
-        <v>184.1593</v>
+        <v>124.0032</v>
       </c>
     </row>
     <row r="66" spans="1:23">
@@ -5288,46 +5255,46 @@
         <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F66">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G66" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="H66">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I66">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J66">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K66">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L66">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M66" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N66">
         <v>866</v>
       </c>
       <c r="O66" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
       </c>
       <c r="Q66" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R66" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S66">
         <v>30.458388</v>
@@ -5336,13 +5303,13 @@
         <v>74.453514</v>
       </c>
       <c r="U66" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V66">
-        <v>42630</v>
+        <v>38086</v>
       </c>
       <c r="W66">
-        <v>184.1593</v>
+        <v>135.8685</v>
       </c>
     </row>
     <row r="67" spans="1:23">
@@ -5359,46 +5326,46 @@
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F67">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G67" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="H67">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I67">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J67">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K67">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L67">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M67" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N67">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="O67" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
       </c>
       <c r="Q67" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R67" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S67">
         <v>30.458388</v>
@@ -5407,13 +5374,13 @@
         <v>74.453514</v>
       </c>
       <c r="U67" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V67">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W67">
-        <v>184.1593</v>
+        <v>135.8685</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -5430,46 +5397,46 @@
         <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F68">
-        <v>1322</v>
+        <v>1597</v>
       </c>
       <c r="G68" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="H68">
-        <v>30.67924</v>
+        <v>30.419565</v>
       </c>
       <c r="I68">
-        <v>75.84139999999999</v>
+        <v>74.44302166999999</v>
       </c>
       <c r="J68">
-        <v>703</v>
+        <v>1455</v>
       </c>
       <c r="K68">
-        <v>30.618135</v>
+        <v>30.450458</v>
       </c>
       <c r="L68">
-        <v>75.435686</v>
+        <v>74.489422</v>
       </c>
       <c r="M68" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N68">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="O68" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
       </c>
       <c r="Q68" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R68" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S68">
         <v>30.458388</v>
@@ -5478,13 +5445,13 @@
         <v>74.453514</v>
       </c>
       <c r="U68" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V68">
-        <v>10000</v>
+        <v>5127</v>
       </c>
       <c r="W68">
-        <v>184.1593</v>
+        <v>135.8685</v>
       </c>
     </row>
     <row r="69" spans="1:23">
@@ -5501,46 +5468,46 @@
         <v>28</v>
       </c>
       <c r="E69" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F69">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G69" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H69">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I69">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J69">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K69">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L69">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M69" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N69">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="O69" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
       </c>
       <c r="Q69" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R69" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S69">
         <v>30.458388</v>
@@ -5549,13 +5516,13 @@
         <v>74.453514</v>
       </c>
       <c r="U69" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V69">
-        <v>10000</v>
+        <v>294680</v>
       </c>
       <c r="W69">
-        <v>184.1593</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="70" spans="1:23">
@@ -5572,46 +5539,46 @@
         <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F70">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G70" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H70">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I70">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J70">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K70">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L70">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M70" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N70">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="O70" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
       </c>
       <c r="Q70" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R70" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S70">
         <v>30.458388</v>
@@ -5620,13 +5587,13 @@
         <v>74.453514</v>
       </c>
       <c r="U70" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V70">
-        <v>30720</v>
+        <v>16680</v>
       </c>
       <c r="W70">
-        <v>184.1593</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="71" spans="1:23">
@@ -5643,46 +5610,46 @@
         <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G71" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H71">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I71">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J71">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K71">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L71">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M71" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N71">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="O71" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
       </c>
       <c r="Q71" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R71" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S71">
         <v>30.458388</v>
@@ -5691,13 +5658,13 @@
         <v>74.453514</v>
       </c>
       <c r="U71" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V71">
-        <v>1080</v>
+        <v>10000</v>
       </c>
       <c r="W71">
-        <v>184.1593</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="72" spans="1:23">
@@ -5714,46 +5681,46 @@
         <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F72">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G72" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H72">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I72">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J72">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K72">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L72">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M72" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N72">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="O72" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
       </c>
       <c r="Q72" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R72" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S72">
         <v>30.458388</v>
@@ -5762,13 +5729,13 @@
         <v>74.453514</v>
       </c>
       <c r="U72" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V72">
-        <v>29640</v>
+        <v>10000</v>
       </c>
       <c r="W72">
-        <v>184.1593</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="73" spans="1:23">
@@ -5785,46 +5752,46 @@
         <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F73">
-        <v>1322</v>
+        <v>1607</v>
       </c>
       <c r="G73" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H73">
-        <v>30.67924</v>
+        <v>30.4726737</v>
       </c>
       <c r="I73">
-        <v>75.84139999999999</v>
+        <v>74.5049465</v>
       </c>
       <c r="J73">
-        <v>703</v>
+        <v>1512</v>
       </c>
       <c r="K73">
-        <v>30.618135</v>
+        <v>30.4713293</v>
       </c>
       <c r="L73">
-        <v>75.435686</v>
+        <v>74.5033904</v>
       </c>
       <c r="M73" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N73">
-        <v>877</v>
+        <v>869</v>
       </c>
       <c r="O73" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
       </c>
       <c r="Q73" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R73" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S73">
         <v>30.458388</v>
@@ -5833,13 +5800,13 @@
         <v>74.453514</v>
       </c>
       <c r="U73" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V73">
-        <v>9950</v>
+        <v>10000</v>
       </c>
       <c r="W73">
-        <v>184.1593</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="74" spans="1:23">
@@ -5856,46 +5823,46 @@
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F74">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G74" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H74">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I74">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J74">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K74">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L74">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M74" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N74">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="O74" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
       </c>
       <c r="Q74" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R74" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S74">
         <v>30.458388</v>
@@ -5904,13 +5871,13 @@
         <v>74.453514</v>
       </c>
       <c r="U74" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V74">
-        <v>10000</v>
+        <v>30720</v>
       </c>
       <c r="W74">
-        <v>350.8759</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="75" spans="1:23">
@@ -5927,46 +5894,46 @@
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F75">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G75" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H75">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I75">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J75">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K75">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L75">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M75" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N75">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="O75" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
       </c>
       <c r="Q75" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R75" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S75">
         <v>30.458388</v>
@@ -5975,13 +5942,13 @@
         <v>74.453514</v>
       </c>
       <c r="U75" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V75">
-        <v>5000</v>
+        <v>29640</v>
       </c>
       <c r="W75">
-        <v>350.8759</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -5998,46 +5965,46 @@
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F76">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G76" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H76">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I76">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J76">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K76">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L76">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M76" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N76">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="O76" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
       </c>
       <c r="Q76" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R76" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S76">
         <v>30.458388</v>
@@ -6046,13 +6013,13 @@
         <v>74.453514</v>
       </c>
       <c r="U76" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V76">
-        <v>5000</v>
+        <v>28460</v>
       </c>
       <c r="W76">
-        <v>350.8759</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="77" spans="1:23">
@@ -6069,46 +6036,46 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F77">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G77" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H77">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I77">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J77">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K77">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L77">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M77" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N77">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="O77" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
       </c>
       <c r="Q77" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R77" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S77">
         <v>30.458388</v>
@@ -6117,13 +6084,13 @@
         <v>74.453514</v>
       </c>
       <c r="U77" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V77">
-        <v>20480</v>
+        <v>15353</v>
       </c>
       <c r="W77">
-        <v>350.8759</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="78" spans="1:23">
@@ -6140,46 +6107,46 @@
         <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F78">
-        <v>1323</v>
+        <v>1607</v>
       </c>
       <c r="G78" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H78">
-        <v>30.61296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I78">
-        <v>75.84106</v>
+        <v>74.5049465</v>
       </c>
       <c r="J78">
-        <v>999</v>
+        <v>1512</v>
       </c>
       <c r="K78">
-        <v>30.561546</v>
+        <v>30.4713293</v>
       </c>
       <c r="L78">
-        <v>75.352118</v>
+        <v>74.5033904</v>
       </c>
       <c r="M78" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N78">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="O78" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
       </c>
       <c r="Q78" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R78" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S78">
         <v>30.458388</v>
@@ -6188,13 +6155,13 @@
         <v>74.453514</v>
       </c>
       <c r="U78" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V78">
-        <v>18000</v>
+        <v>20480</v>
       </c>
       <c r="W78">
-        <v>350.8759</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="79" spans="1:23">
@@ -6211,46 +6178,46 @@
         <v>28</v>
       </c>
       <c r="E79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F79">
-        <v>1324</v>
+        <v>1607</v>
       </c>
       <c r="G79" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H79">
-        <v>30.59296</v>
+        <v>30.4726737</v>
       </c>
       <c r="I79">
-        <v>75.78903</v>
+        <v>74.5049465</v>
       </c>
       <c r="J79">
-        <v>216</v>
+        <v>1512</v>
       </c>
       <c r="K79">
-        <v>30.5076194</v>
+        <v>30.4713293</v>
       </c>
       <c r="L79">
-        <v>74.958715</v>
+        <v>74.5033904</v>
       </c>
       <c r="M79" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N79">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="O79" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
       </c>
       <c r="Q79" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R79" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S79">
         <v>30.458388</v>
@@ -6259,13 +6226,13 @@
         <v>74.453514</v>
       </c>
       <c r="U79" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V79">
-        <v>41830</v>
+        <v>20480</v>
       </c>
       <c r="W79">
-        <v>122.5477</v>
+        <v>154.1812</v>
       </c>
     </row>
     <row r="80" spans="1:23">
@@ -6282,46 +6249,46 @@
         <v>28</v>
       </c>
       <c r="E80" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F80">
-        <v>1325</v>
+        <v>1607</v>
       </c>
       <c r="G80" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H80">
-        <v>30.61907</v>
+        <v>30.4726737</v>
       </c>
       <c r="I80">
-        <v>75.8098</v>
+        <v>74.5049465</v>
       </c>
       <c r="J80">
-        <v>217</v>
+        <v>1512</v>
       </c>
       <c r="K80">
-        <v>30.51445</v>
+        <v>30.4713293</v>
       </c>
       <c r="L80">
-        <v>74.89836</v>
+        <v>74.5033904</v>
       </c>
       <c r="M80" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="N80">
-        <v>864</v>
+        <v>880</v>
       </c>
       <c r="O80" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
       </c>
       <c r="Q80" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="R80" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S80">
         <v>30.458388</v>
@@ -6330,652 +6297,13 @@
         <v>74.453514</v>
       </c>
       <c r="U80" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="V80">
-        <v>55220</v>
+        <v>15360</v>
       </c>
       <c r="W80">
-        <v>96.983</v>
-      </c>
-    </row>
-    <row r="81" spans="1:23">
-      <c r="A81" t="s">
-        <v>23</v>
-      </c>
-      <c r="B81" t="s">
-        <v>24</v>
-      </c>
-      <c r="C81" t="s">
-        <v>25</v>
-      </c>
-      <c r="D81" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" t="s">
-        <v>32</v>
-      </c>
-      <c r="F81">
-        <v>1326</v>
-      </c>
-      <c r="G81" t="s">
-        <v>86</v>
-      </c>
-      <c r="H81">
-        <v>30.60582</v>
-      </c>
-      <c r="I81">
-        <v>75.87558</v>
-      </c>
-      <c r="J81">
-        <v>57</v>
-      </c>
-      <c r="K81">
-        <v>30.58822</v>
-      </c>
-      <c r="L81">
-        <v>75.6722</v>
-      </c>
-      <c r="M81" t="s">
-        <v>92</v>
-      </c>
-      <c r="N81">
-        <v>866</v>
-      </c>
-      <c r="O81" t="s">
-        <v>93</v>
-      </c>
-      <c r="P81" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>28</v>
-      </c>
-      <c r="R81" t="s">
-        <v>32</v>
-      </c>
-      <c r="S81">
-        <v>30.458388</v>
-      </c>
-      <c r="T81">
-        <v>74.453514</v>
-      </c>
-      <c r="U81" t="s">
-        <v>94</v>
-      </c>
-      <c r="V81">
-        <v>13140</v>
-      </c>
-      <c r="W81">
-        <v>371.6053</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23">
-      <c r="A82" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" t="s">
-        <v>25</v>
-      </c>
-      <c r="D82" t="s">
-        <v>28</v>
-      </c>
-      <c r="E82" t="s">
-        <v>32</v>
-      </c>
-      <c r="F82">
-        <v>1326</v>
-      </c>
-      <c r="G82" t="s">
-        <v>86</v>
-      </c>
-      <c r="H82">
-        <v>30.60582</v>
-      </c>
-      <c r="I82">
-        <v>75.87558</v>
-      </c>
-      <c r="J82">
-        <v>57</v>
-      </c>
-      <c r="K82">
-        <v>30.58822</v>
-      </c>
-      <c r="L82">
-        <v>75.6722</v>
-      </c>
-      <c r="M82" t="s">
-        <v>92</v>
-      </c>
-      <c r="N82">
-        <v>874</v>
-      </c>
-      <c r="O82" t="s">
-        <v>93</v>
-      </c>
-      <c r="P82" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>28</v>
-      </c>
-      <c r="R82" t="s">
-        <v>32</v>
-      </c>
-      <c r="S82">
-        <v>30.458388</v>
-      </c>
-      <c r="T82">
-        <v>74.453514</v>
-      </c>
-      <c r="U82" t="s">
-        <v>94</v>
-      </c>
-      <c r="V82">
-        <v>28460</v>
-      </c>
-      <c r="W82">
-        <v>371.6053</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23">
-      <c r="A83" t="s">
-        <v>23</v>
-      </c>
-      <c r="B83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" t="s">
-        <v>25</v>
-      </c>
-      <c r="D83" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" t="s">
-        <v>32</v>
-      </c>
-      <c r="F83">
-        <v>1326</v>
-      </c>
-      <c r="G83" t="s">
-        <v>86</v>
-      </c>
-      <c r="H83">
-        <v>30.60582</v>
-      </c>
-      <c r="I83">
-        <v>75.87558</v>
-      </c>
-      <c r="J83">
-        <v>57</v>
-      </c>
-      <c r="K83">
-        <v>30.58822</v>
-      </c>
-      <c r="L83">
-        <v>75.6722</v>
-      </c>
-      <c r="M83" t="s">
-        <v>92</v>
-      </c>
-      <c r="N83">
-        <v>879</v>
-      </c>
-      <c r="O83" t="s">
-        <v>93</v>
-      </c>
-      <c r="P83" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>28</v>
-      </c>
-      <c r="R83" t="s">
-        <v>32</v>
-      </c>
-      <c r="S83">
-        <v>30.458388</v>
-      </c>
-      <c r="T83">
-        <v>74.453514</v>
-      </c>
-      <c r="U83" t="s">
-        <v>94</v>
-      </c>
-      <c r="V83">
-        <v>2480</v>
-      </c>
-      <c r="W83">
-        <v>371.6053</v>
-      </c>
-    </row>
-    <row r="84" spans="1:23">
-      <c r="A84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" t="s">
-        <v>25</v>
-      </c>
-      <c r="D84" t="s">
-        <v>28</v>
-      </c>
-      <c r="E84" t="s">
-        <v>32</v>
-      </c>
-      <c r="F84">
-        <v>1327</v>
-      </c>
-      <c r="G84" t="s">
-        <v>87</v>
-      </c>
-      <c r="H84">
-        <v>30.62411</v>
-      </c>
-      <c r="I84">
-        <v>75.75073</v>
-      </c>
-      <c r="J84">
-        <v>217</v>
-      </c>
-      <c r="K84">
-        <v>30.51445</v>
-      </c>
-      <c r="L84">
-        <v>74.89836</v>
-      </c>
-      <c r="M84" t="s">
-        <v>92</v>
-      </c>
-      <c r="N84">
-        <v>866</v>
-      </c>
-      <c r="O84" t="s">
-        <v>93</v>
-      </c>
-      <c r="P84" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" t="s">
-        <v>28</v>
-      </c>
-      <c r="R84" t="s">
-        <v>32</v>
-      </c>
-      <c r="S84">
-        <v>30.458388</v>
-      </c>
-      <c r="T84">
-        <v>74.453514</v>
-      </c>
-      <c r="U84" t="s">
-        <v>94</v>
-      </c>
-      <c r="V84">
-        <v>59240</v>
-      </c>
-      <c r="W84">
-        <v>96.983</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23">
-      <c r="A85" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" t="s">
-        <v>25</v>
-      </c>
-      <c r="D85" t="s">
-        <v>28</v>
-      </c>
-      <c r="E85" t="s">
-        <v>32</v>
-      </c>
-      <c r="F85">
-        <v>1328</v>
-      </c>
-      <c r="G85" t="s">
-        <v>88</v>
-      </c>
-      <c r="H85">
-        <v>30.58776</v>
-      </c>
-      <c r="I85">
-        <v>75.81787</v>
-      </c>
-      <c r="J85">
-        <v>216</v>
-      </c>
-      <c r="K85">
-        <v>30.5076194</v>
-      </c>
-      <c r="L85">
-        <v>74.958715</v>
-      </c>
-      <c r="M85" t="s">
-        <v>92</v>
-      </c>
-      <c r="N85">
-        <v>866</v>
-      </c>
-      <c r="O85" t="s">
-        <v>93</v>
-      </c>
-      <c r="P85" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>28</v>
-      </c>
-      <c r="R85" t="s">
-        <v>32</v>
-      </c>
-      <c r="S85">
-        <v>30.458388</v>
-      </c>
-      <c r="T85">
-        <v>74.453514</v>
-      </c>
-      <c r="U85" t="s">
-        <v>94</v>
-      </c>
-      <c r="V85">
-        <v>11670</v>
-      </c>
-      <c r="W85">
-        <v>104.0333</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23">
-      <c r="A86" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" t="s">
-        <v>25</v>
-      </c>
-      <c r="D86" t="s">
-        <v>28</v>
-      </c>
-      <c r="E86" t="s">
-        <v>32</v>
-      </c>
-      <c r="F86">
-        <v>1328</v>
-      </c>
-      <c r="G86" t="s">
-        <v>88</v>
-      </c>
-      <c r="H86">
-        <v>30.58776</v>
-      </c>
-      <c r="I86">
-        <v>75.81787</v>
-      </c>
-      <c r="J86">
-        <v>216</v>
-      </c>
-      <c r="K86">
-        <v>30.5076194</v>
-      </c>
-      <c r="L86">
-        <v>74.958715</v>
-      </c>
-      <c r="M86" t="s">
-        <v>92</v>
-      </c>
-      <c r="N86">
-        <v>880</v>
-      </c>
-      <c r="O86" t="s">
-        <v>93</v>
-      </c>
-      <c r="P86" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>28</v>
-      </c>
-      <c r="R86" t="s">
-        <v>32</v>
-      </c>
-      <c r="S86">
-        <v>30.458388</v>
-      </c>
-      <c r="T86">
-        <v>74.453514</v>
-      </c>
-      <c r="U86" t="s">
-        <v>94</v>
-      </c>
-      <c r="V86">
-        <v>15360</v>
-      </c>
-      <c r="W86">
-        <v>104.0333</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23">
-      <c r="A87" t="s">
-        <v>23</v>
-      </c>
-      <c r="B87" t="s">
-        <v>24</v>
-      </c>
-      <c r="C87" t="s">
-        <v>25</v>
-      </c>
-      <c r="D87" t="s">
-        <v>28</v>
-      </c>
-      <c r="E87" t="s">
-        <v>32</v>
-      </c>
-      <c r="F87">
-        <v>1329</v>
-      </c>
-      <c r="G87" t="s">
-        <v>89</v>
-      </c>
-      <c r="H87">
-        <v>30.669134</v>
-      </c>
-      <c r="I87">
-        <v>75.877723</v>
-      </c>
-      <c r="J87">
-        <v>678</v>
-      </c>
-      <c r="K87">
-        <v>30.633572</v>
-      </c>
-      <c r="L87">
-        <v>75.628421</v>
-      </c>
-      <c r="M87" t="s">
-        <v>92</v>
-      </c>
-      <c r="N87">
-        <v>877</v>
-      </c>
-      <c r="O87" t="s">
-        <v>93</v>
-      </c>
-      <c r="P87" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>28</v>
-      </c>
-      <c r="R87" t="s">
-        <v>32</v>
-      </c>
-      <c r="S87">
-        <v>30.458388</v>
-      </c>
-      <c r="T87">
-        <v>74.453514</v>
-      </c>
-      <c r="U87" t="s">
-        <v>94</v>
-      </c>
-      <c r="V87">
-        <v>10530</v>
-      </c>
-      <c r="W87">
-        <v>238.155</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23">
-      <c r="A88" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" t="s">
-        <v>24</v>
-      </c>
-      <c r="C88" t="s">
-        <v>25</v>
-      </c>
-      <c r="D88" t="s">
-        <v>28</v>
-      </c>
-      <c r="E88" t="s">
-        <v>32</v>
-      </c>
-      <c r="F88">
-        <v>1330</v>
-      </c>
-      <c r="G88" t="s">
-        <v>90</v>
-      </c>
-      <c r="H88">
-        <v>30.651445</v>
-      </c>
-      <c r="I88">
-        <v>75.890028</v>
-      </c>
-      <c r="J88">
-        <v>1225</v>
-      </c>
-      <c r="K88">
-        <v>30.5792101</v>
-      </c>
-      <c r="L88">
-        <v>75.30097960000001</v>
-      </c>
-      <c r="M88" t="s">
-        <v>92</v>
-      </c>
-      <c r="N88">
-        <v>872</v>
-      </c>
-      <c r="O88" t="s">
-        <v>93</v>
-      </c>
-      <c r="P88" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>28</v>
-      </c>
-      <c r="R88" t="s">
-        <v>32</v>
-      </c>
-      <c r="S88">
-        <v>30.458388</v>
-      </c>
-      <c r="T88">
-        <v>74.453514</v>
-      </c>
-      <c r="U88" t="s">
-        <v>94</v>
-      </c>
-      <c r="V88">
-        <v>29640</v>
-      </c>
-      <c r="W88">
-        <v>307.8293</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23">
-      <c r="A89" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" t="s">
-        <v>24</v>
-      </c>
-      <c r="C89" t="s">
-        <v>25</v>
-      </c>
-      <c r="D89" t="s">
-        <v>29</v>
-      </c>
-      <c r="E89" t="s">
-        <v>33</v>
-      </c>
-      <c r="F89">
-        <v>1660</v>
-      </c>
-      <c r="G89" t="s">
-        <v>91</v>
-      </c>
-      <c r="H89">
-        <v>30.2397029</v>
-      </c>
-      <c r="I89">
-        <v>74.2953411</v>
-      </c>
-      <c r="J89">
-        <v>287</v>
-      </c>
-      <c r="K89">
-        <v>30.126927</v>
-      </c>
-      <c r="L89">
-        <v>74.161942</v>
-      </c>
-      <c r="M89" t="s">
-        <v>92</v>
-      </c>
-      <c r="N89">
-        <v>407</v>
-      </c>
-      <c r="O89" t="s">
-        <v>93</v>
-      </c>
-      <c r="P89" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>26</v>
-      </c>
-      <c r="R89" t="s">
-        <v>30</v>
-      </c>
-      <c r="S89">
-        <v>30.126927</v>
-      </c>
-      <c r="T89">
-        <v>74.161942</v>
-      </c>
-      <c r="U89" t="s">
-        <v>94</v>
-      </c>
-      <c r="V89">
-        <v>15621</v>
-      </c>
-      <c r="W89">
-        <v>205.7123</v>
+        <v>154.1812</v>
       </c>
     </row>
   </sheetData>
